--- a/Odds-Data-Clean/2007-08.xlsx
+++ b/Odds-Data-Clean/2007-08.xlsx
@@ -19566,7 +19566,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>2007-08-102</t>
+          <t>2007-08-0102</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -19608,7 +19608,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>2007-08-102</t>
+          <t>2007-08-0102</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -19650,7 +19650,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>2007-08-102</t>
+          <t>2007-08-0102</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -19692,7 +19692,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>2007-08-102</t>
+          <t>2007-08-0102</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -19734,7 +19734,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>2007-08-102</t>
+          <t>2007-08-0102</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -19776,7 +19776,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>2007-08-102</t>
+          <t>2007-08-0102</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -19818,7 +19818,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>2007-08-102</t>
+          <t>2007-08-0102</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -19860,7 +19860,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>2007-08-102</t>
+          <t>2007-08-0102</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -19902,7 +19902,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>2007-08-102</t>
+          <t>2007-08-0102</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -19944,7 +19944,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>2007-08-102</t>
+          <t>2007-08-0102</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -19986,7 +19986,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>2007-08-102</t>
+          <t>2007-08-0102</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -20028,7 +20028,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>2007-08-102</t>
+          <t>2007-08-0102</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -20070,7 +20070,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>2007-08-103</t>
+          <t>2007-08-0103</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -20112,7 +20112,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>2007-08-103</t>
+          <t>2007-08-0103</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -20154,7 +20154,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>2007-08-103</t>
+          <t>2007-08-0103</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -20196,7 +20196,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>2007-08-104</t>
+          <t>2007-08-0104</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -20238,7 +20238,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>2007-08-104</t>
+          <t>2007-08-0104</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -20280,7 +20280,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>2007-08-104</t>
+          <t>2007-08-0104</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -20322,7 +20322,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>2007-08-104</t>
+          <t>2007-08-0104</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -20364,7 +20364,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>2007-08-104</t>
+          <t>2007-08-0104</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -20406,7 +20406,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>2007-08-104</t>
+          <t>2007-08-0104</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -20448,7 +20448,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>2007-08-104</t>
+          <t>2007-08-0104</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -20490,7 +20490,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>2007-08-104</t>
+          <t>2007-08-0104</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -20532,7 +20532,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>2007-08-104</t>
+          <t>2007-08-0104</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -20574,7 +20574,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>2007-08-104</t>
+          <t>2007-08-0104</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -20616,7 +20616,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>2007-08-104</t>
+          <t>2007-08-0104</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -20658,7 +20658,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>2007-08-104</t>
+          <t>2007-08-0104</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -20700,7 +20700,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>2007-08-105</t>
+          <t>2007-08-0105</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -20742,7 +20742,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>2007-08-105</t>
+          <t>2007-08-0105</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -20784,7 +20784,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>2007-08-105</t>
+          <t>2007-08-0105</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -20826,7 +20826,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>2007-08-105</t>
+          <t>2007-08-0105</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -20868,7 +20868,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>2007-08-105</t>
+          <t>2007-08-0105</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -20910,7 +20910,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>2007-08-105</t>
+          <t>2007-08-0105</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -20952,7 +20952,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>2007-08-106</t>
+          <t>2007-08-0106</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -20994,7 +20994,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>2007-08-106</t>
+          <t>2007-08-0106</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -21036,7 +21036,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>2007-08-106</t>
+          <t>2007-08-0106</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -21078,7 +21078,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>2007-08-106</t>
+          <t>2007-08-0106</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -21120,7 +21120,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>2007-08-106</t>
+          <t>2007-08-0106</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -21162,7 +21162,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>2007-08-106</t>
+          <t>2007-08-0106</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -21204,7 +21204,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>2007-08-106</t>
+          <t>2007-08-0106</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -21246,7 +21246,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>2007-08-106</t>
+          <t>2007-08-0106</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -21288,7 +21288,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>2007-08-107</t>
+          <t>2007-08-0107</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -21330,7 +21330,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>2007-08-107</t>
+          <t>2007-08-0107</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -21372,7 +21372,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>2007-08-108</t>
+          <t>2007-08-0108</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -21414,7 +21414,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>2007-08-108</t>
+          <t>2007-08-0108</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -21456,7 +21456,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>2007-08-108</t>
+          <t>2007-08-0108</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -21498,7 +21498,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>2007-08-108</t>
+          <t>2007-08-0108</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -21540,7 +21540,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>2007-08-108</t>
+          <t>2007-08-0108</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -21582,7 +21582,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>2007-08-108</t>
+          <t>2007-08-0108</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -21624,7 +21624,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>2007-08-108</t>
+          <t>2007-08-0108</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -21666,7 +21666,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>2007-08-108</t>
+          <t>2007-08-0108</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -21708,7 +21708,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>2007-08-108</t>
+          <t>2007-08-0108</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -21750,7 +21750,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>2007-08-109</t>
+          <t>2007-08-0109</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -21792,7 +21792,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>2007-08-109</t>
+          <t>2007-08-0109</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -21834,7 +21834,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>2007-08-109</t>
+          <t>2007-08-0109</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -21876,7 +21876,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>2007-08-109</t>
+          <t>2007-08-0109</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -21918,7 +21918,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>2007-08-109</t>
+          <t>2007-08-0109</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -21960,7 +21960,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>2007-08-109</t>
+          <t>2007-08-0109</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -22002,7 +22002,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>2007-08-109</t>
+          <t>2007-08-0109</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -22044,7 +22044,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>2007-08-109</t>
+          <t>2007-08-0109</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -22086,7 +22086,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>2007-08-109</t>
+          <t>2007-08-0109</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -22128,7 +22128,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>2007-08-109</t>
+          <t>2007-08-0109</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -22170,7 +22170,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>2007-08-109</t>
+          <t>2007-08-0109</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -22212,7 +22212,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>2007-08-110</t>
+          <t>2007-08-0110</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -22254,7 +22254,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>2007-08-110</t>
+          <t>2007-08-0110</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -22296,7 +22296,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>2007-08-110</t>
+          <t>2007-08-0110</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -22338,7 +22338,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>2007-08-111</t>
+          <t>2007-08-0111</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -22380,7 +22380,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>2007-08-111</t>
+          <t>2007-08-0111</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -22422,7 +22422,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>2007-08-111</t>
+          <t>2007-08-0111</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -22464,7 +22464,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>2007-08-111</t>
+          <t>2007-08-0111</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -22506,7 +22506,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>2007-08-111</t>
+          <t>2007-08-0111</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -22548,7 +22548,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>2007-08-111</t>
+          <t>2007-08-0111</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -22590,7 +22590,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>2007-08-111</t>
+          <t>2007-08-0111</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -22632,7 +22632,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>2007-08-111</t>
+          <t>2007-08-0111</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -22674,7 +22674,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>2007-08-111</t>
+          <t>2007-08-0111</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -22716,7 +22716,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>2007-08-111</t>
+          <t>2007-08-0111</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -22758,7 +22758,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>2007-08-111</t>
+          <t>2007-08-0111</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -22800,7 +22800,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>2007-08-112</t>
+          <t>2007-08-0112</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -22842,7 +22842,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>2007-08-112</t>
+          <t>2007-08-0112</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -22884,7 +22884,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>2007-08-112</t>
+          <t>2007-08-0112</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -22926,7 +22926,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>2007-08-112</t>
+          <t>2007-08-0112</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -22968,7 +22968,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>2007-08-112</t>
+          <t>2007-08-0112</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -23010,7 +23010,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>2007-08-112</t>
+          <t>2007-08-0112</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -23052,7 +23052,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>2007-08-112</t>
+          <t>2007-08-0112</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -23094,7 +23094,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>2007-08-113</t>
+          <t>2007-08-0113</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -23136,7 +23136,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>2007-08-113</t>
+          <t>2007-08-0113</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -23178,7 +23178,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>2007-08-113</t>
+          <t>2007-08-0113</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -23220,7 +23220,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>2007-08-113</t>
+          <t>2007-08-0113</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -23262,7 +23262,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>2007-08-113</t>
+          <t>2007-08-0113</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -23304,7 +23304,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>2007-08-113</t>
+          <t>2007-08-0113</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -23346,7 +23346,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>2007-08-114</t>
+          <t>2007-08-0114</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -23388,7 +23388,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>2007-08-114</t>
+          <t>2007-08-0114</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -23430,7 +23430,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>2007-08-114</t>
+          <t>2007-08-0114</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -23472,7 +23472,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>2007-08-114</t>
+          <t>2007-08-0114</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -23514,7 +23514,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>2007-08-114</t>
+          <t>2007-08-0114</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -23556,7 +23556,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>2007-08-114</t>
+          <t>2007-08-0114</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -23598,7 +23598,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>2007-08-114</t>
+          <t>2007-08-0114</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -23640,7 +23640,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>2007-08-115</t>
+          <t>2007-08-0115</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -23682,7 +23682,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>2007-08-115</t>
+          <t>2007-08-0115</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>2007-08-115</t>
+          <t>2007-08-0115</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -23766,7 +23766,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>2007-08-115</t>
+          <t>2007-08-0115</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -23808,7 +23808,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>2007-08-115</t>
+          <t>2007-08-0115</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -23850,7 +23850,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>2007-08-115</t>
+          <t>2007-08-0115</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -23892,7 +23892,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>2007-08-115</t>
+          <t>2007-08-0115</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -23934,7 +23934,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>2007-08-115</t>
+          <t>2007-08-0115</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -23976,7 +23976,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>2007-08-116</t>
+          <t>2007-08-0116</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -24018,7 +24018,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>2007-08-116</t>
+          <t>2007-08-0116</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -24060,7 +24060,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>2007-08-116</t>
+          <t>2007-08-0116</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -24102,7 +24102,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>2007-08-116</t>
+          <t>2007-08-0116</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -24144,7 +24144,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>2007-08-116</t>
+          <t>2007-08-0116</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -24186,7 +24186,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>2007-08-116</t>
+          <t>2007-08-0116</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -24228,7 +24228,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>2007-08-116</t>
+          <t>2007-08-0116</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -24270,7 +24270,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>2007-08-116</t>
+          <t>2007-08-0116</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -24312,7 +24312,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>2007-08-117</t>
+          <t>2007-08-0117</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -24354,7 +24354,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>2007-08-117</t>
+          <t>2007-08-0117</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -24396,7 +24396,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>2007-08-117</t>
+          <t>2007-08-0117</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -24438,7 +24438,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>2007-08-118</t>
+          <t>2007-08-0118</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -24480,7 +24480,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>2007-08-118</t>
+          <t>2007-08-0118</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -24522,7 +24522,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>2007-08-118</t>
+          <t>2007-08-0118</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -24564,7 +24564,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>2007-08-118</t>
+          <t>2007-08-0118</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -24606,7 +24606,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>2007-08-118</t>
+          <t>2007-08-0118</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -24648,7 +24648,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>2007-08-118</t>
+          <t>2007-08-0118</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -24690,7 +24690,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>2007-08-118</t>
+          <t>2007-08-0118</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -24732,7 +24732,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>2007-08-118</t>
+          <t>2007-08-0118</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -24774,7 +24774,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>2007-08-118</t>
+          <t>2007-08-0118</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -24816,7 +24816,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>2007-08-118</t>
+          <t>2007-08-0118</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -24858,7 +24858,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>2007-08-119</t>
+          <t>2007-08-0119</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -24900,7 +24900,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>2007-08-119</t>
+          <t>2007-08-0119</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -24942,7 +24942,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>2007-08-119</t>
+          <t>2007-08-0119</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>2007-08-119</t>
+          <t>2007-08-0119</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -25026,7 +25026,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>2007-08-119</t>
+          <t>2007-08-0119</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -25068,7 +25068,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>2007-08-119</t>
+          <t>2007-08-0119</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -25110,7 +25110,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>2007-08-119</t>
+          <t>2007-08-0119</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -25152,7 +25152,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>2007-08-119</t>
+          <t>2007-08-0119</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -25194,7 +25194,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>2007-08-119</t>
+          <t>2007-08-0119</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -25236,7 +25236,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>2007-08-119</t>
+          <t>2007-08-0119</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -25278,7 +25278,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>2007-08-119</t>
+          <t>2007-08-0119</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -25320,7 +25320,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>2007-08-120</t>
+          <t>2007-08-0120</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -25362,7 +25362,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>2007-08-121</t>
+          <t>2007-08-0121</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -25404,7 +25404,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>2007-08-121</t>
+          <t>2007-08-0121</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -25446,7 +25446,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>2007-08-121</t>
+          <t>2007-08-0121</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -25488,7 +25488,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>2007-08-121</t>
+          <t>2007-08-0121</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -25530,7 +25530,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>2007-08-121</t>
+          <t>2007-08-0121</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -25572,7 +25572,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>2007-08-121</t>
+          <t>2007-08-0121</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -25614,7 +25614,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>2007-08-121</t>
+          <t>2007-08-0121</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -25656,7 +25656,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>2007-08-121</t>
+          <t>2007-08-0121</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -25698,7 +25698,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>2007-08-121</t>
+          <t>2007-08-0121</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -25740,7 +25740,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>2007-08-121</t>
+          <t>2007-08-0121</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -25782,7 +25782,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>2007-08-121</t>
+          <t>2007-08-0121</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -25824,7 +25824,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>2007-08-121</t>
+          <t>2007-08-0121</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -25866,7 +25866,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>2007-08-121</t>
+          <t>2007-08-0121</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -25908,7 +25908,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>2007-08-122</t>
+          <t>2007-08-0122</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -25950,7 +25950,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>2007-08-122</t>
+          <t>2007-08-0122</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -25992,7 +25992,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>2007-08-123</t>
+          <t>2007-08-0123</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -26034,7 +26034,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>2007-08-123</t>
+          <t>2007-08-0123</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -26076,7 +26076,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>2007-08-123</t>
+          <t>2007-08-0123</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -26118,7 +26118,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>2007-08-123</t>
+          <t>2007-08-0123</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -26160,7 +26160,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>2007-08-123</t>
+          <t>2007-08-0123</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -26202,7 +26202,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>2007-08-123</t>
+          <t>2007-08-0123</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -26244,7 +26244,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>2007-08-123</t>
+          <t>2007-08-0123</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -26286,7 +26286,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>2007-08-123</t>
+          <t>2007-08-0123</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -26328,7 +26328,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>2007-08-123</t>
+          <t>2007-08-0123</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -26370,7 +26370,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>2007-08-123</t>
+          <t>2007-08-0123</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -26412,7 +26412,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>2007-08-123</t>
+          <t>2007-08-0123</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -26454,7 +26454,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>2007-08-123</t>
+          <t>2007-08-0123</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -26496,7 +26496,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>2007-08-124</t>
+          <t>2007-08-0124</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -26538,7 +26538,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>2007-08-124</t>
+          <t>2007-08-0124</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -26580,7 +26580,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>2007-08-124</t>
+          <t>2007-08-0124</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -26622,7 +26622,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>2007-08-125</t>
+          <t>2007-08-0125</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -26664,7 +26664,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>2007-08-125</t>
+          <t>2007-08-0125</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -26706,7 +26706,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>2007-08-125</t>
+          <t>2007-08-0125</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -26748,7 +26748,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>2007-08-125</t>
+          <t>2007-08-0125</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -26790,7 +26790,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>2007-08-125</t>
+          <t>2007-08-0125</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -26832,7 +26832,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>2007-08-125</t>
+          <t>2007-08-0125</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -26874,7 +26874,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>2007-08-125</t>
+          <t>2007-08-0125</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -26916,7 +26916,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>2007-08-125</t>
+          <t>2007-08-0125</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -26958,7 +26958,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>2007-08-125</t>
+          <t>2007-08-0125</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -27000,7 +27000,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>2007-08-125</t>
+          <t>2007-08-0125</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -27042,7 +27042,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>2007-08-125</t>
+          <t>2007-08-0125</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -27084,7 +27084,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>2007-08-125</t>
+          <t>2007-08-0125</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -27126,7 +27126,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>2007-08-125</t>
+          <t>2007-08-0125</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -27168,7 +27168,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>2007-08-126</t>
+          <t>2007-08-0126</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -27210,7 +27210,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>2007-08-126</t>
+          <t>2007-08-0126</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -27252,7 +27252,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>2007-08-126</t>
+          <t>2007-08-0126</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -27294,7 +27294,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>2007-08-126</t>
+          <t>2007-08-0126</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -27336,7 +27336,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>2007-08-127</t>
+          <t>2007-08-0127</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -27378,7 +27378,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>2007-08-127</t>
+          <t>2007-08-0127</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -27420,7 +27420,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>2007-08-127</t>
+          <t>2007-08-0127</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -27462,7 +27462,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>2007-08-127</t>
+          <t>2007-08-0127</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -27504,7 +27504,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>2007-08-127</t>
+          <t>2007-08-0127</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -27546,7 +27546,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>2007-08-127</t>
+          <t>2007-08-0127</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -27588,7 +27588,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>2007-08-127</t>
+          <t>2007-08-0127</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -27630,7 +27630,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>2007-08-127</t>
+          <t>2007-08-0127</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -27672,7 +27672,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>2007-08-127</t>
+          <t>2007-08-0127</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -27714,7 +27714,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>2007-08-127</t>
+          <t>2007-08-0127</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -27756,7 +27756,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>2007-08-128</t>
+          <t>2007-08-0128</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -27798,7 +27798,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>2007-08-128</t>
+          <t>2007-08-0128</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -27840,7 +27840,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>2007-08-128</t>
+          <t>2007-08-0128</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -27882,7 +27882,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>2007-08-128</t>
+          <t>2007-08-0128</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -27924,7 +27924,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>2007-08-129</t>
+          <t>2007-08-0129</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -27966,7 +27966,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>2007-08-129</t>
+          <t>2007-08-0129</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -28008,7 +28008,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>2007-08-129</t>
+          <t>2007-08-0129</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -28050,7 +28050,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>2007-08-129</t>
+          <t>2007-08-0129</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -28092,7 +28092,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>2007-08-129</t>
+          <t>2007-08-0129</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -28134,7 +28134,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>2007-08-129</t>
+          <t>2007-08-0129</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -28176,7 +28176,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>2007-08-129</t>
+          <t>2007-08-0129</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -28218,7 +28218,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>2007-08-129</t>
+          <t>2007-08-0129</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -28260,7 +28260,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>2007-08-129</t>
+          <t>2007-08-0129</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -28302,7 +28302,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>2007-08-130</t>
+          <t>2007-08-0130</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -28344,7 +28344,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>2007-08-130</t>
+          <t>2007-08-0130</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -28386,7 +28386,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>2007-08-130</t>
+          <t>2007-08-0130</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -28428,7 +28428,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>2007-08-130</t>
+          <t>2007-08-0130</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -28470,7 +28470,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>2007-08-130</t>
+          <t>2007-08-0130</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -28512,7 +28512,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>2007-08-130</t>
+          <t>2007-08-0130</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -28554,7 +28554,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>2007-08-130</t>
+          <t>2007-08-0130</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -28596,7 +28596,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>2007-08-130</t>
+          <t>2007-08-0130</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -28638,7 +28638,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>2007-08-130</t>
+          <t>2007-08-0130</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -28680,7 +28680,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>2007-08-130</t>
+          <t>2007-08-0130</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -28722,7 +28722,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>2007-08-131</t>
+          <t>2007-08-0131</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -28764,7 +28764,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>2007-08-131</t>
+          <t>2007-08-0131</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -28806,7 +28806,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>2007-08-131</t>
+          <t>2007-08-0131</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -28848,7 +28848,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>2007-08-131</t>
+          <t>2007-08-0131</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -28890,7 +28890,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>2007-08-201</t>
+          <t>2007-08-0201</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -28932,7 +28932,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>2007-08-201</t>
+          <t>2007-08-0201</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -28974,7 +28974,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>2007-08-201</t>
+          <t>2007-08-0201</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -29016,7 +29016,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>2007-08-201</t>
+          <t>2007-08-0201</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -29058,7 +29058,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>2007-08-201</t>
+          <t>2007-08-0201</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -29100,7 +29100,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>2007-08-201</t>
+          <t>2007-08-0201</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -29142,7 +29142,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>2007-08-201</t>
+          <t>2007-08-0201</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -29184,7 +29184,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>2007-08-201</t>
+          <t>2007-08-0201</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -29226,7 +29226,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>2007-08-201</t>
+          <t>2007-08-0201</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -29268,7 +29268,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>2007-08-202</t>
+          <t>2007-08-0202</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -29310,7 +29310,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>2007-08-202</t>
+          <t>2007-08-0202</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -29352,7 +29352,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>2007-08-202</t>
+          <t>2007-08-0202</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -29394,7 +29394,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>2007-08-202</t>
+          <t>2007-08-0202</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -29436,7 +29436,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>2007-08-202</t>
+          <t>2007-08-0202</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -29478,7 +29478,7 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>2007-08-202</t>
+          <t>2007-08-0202</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -29520,7 +29520,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>2007-08-202</t>
+          <t>2007-08-0202</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -29562,7 +29562,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>2007-08-202</t>
+          <t>2007-08-0202</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -29604,7 +29604,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>2007-08-203</t>
+          <t>2007-08-0203</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -29646,7 +29646,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>2007-08-203</t>
+          <t>2007-08-0203</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -29688,7 +29688,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>2007-08-204</t>
+          <t>2007-08-0204</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -29730,7 +29730,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>2007-08-204</t>
+          <t>2007-08-0204</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -29772,7 +29772,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>2007-08-204</t>
+          <t>2007-08-0204</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -29814,7 +29814,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>2007-08-204</t>
+          <t>2007-08-0204</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -29856,7 +29856,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>2007-08-204</t>
+          <t>2007-08-0204</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -29898,7 +29898,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>2007-08-204</t>
+          <t>2007-08-0204</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -29940,7 +29940,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>2007-08-204</t>
+          <t>2007-08-0204</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -29982,7 +29982,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>2007-08-204</t>
+          <t>2007-08-0204</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -30024,7 +30024,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>2007-08-204</t>
+          <t>2007-08-0204</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -30066,7 +30066,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>2007-08-205</t>
+          <t>2007-08-0205</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -30108,7 +30108,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>2007-08-205</t>
+          <t>2007-08-0205</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -30150,7 +30150,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>2007-08-205</t>
+          <t>2007-08-0205</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -30192,7 +30192,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>2007-08-205</t>
+          <t>2007-08-0205</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -30234,7 +30234,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>2007-08-205</t>
+          <t>2007-08-0205</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -30276,7 +30276,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>2007-08-206</t>
+          <t>2007-08-0206</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -30318,7 +30318,7 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>2007-08-206</t>
+          <t>2007-08-0206</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -30360,7 +30360,7 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>2007-08-206</t>
+          <t>2007-08-0206</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -30402,7 +30402,7 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>2007-08-206</t>
+          <t>2007-08-0206</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -30444,7 +30444,7 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>2007-08-206</t>
+          <t>2007-08-0206</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -30486,7 +30486,7 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>2007-08-206</t>
+          <t>2007-08-0206</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -30528,7 +30528,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>2007-08-206</t>
+          <t>2007-08-0206</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -30570,7 +30570,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>2007-08-206</t>
+          <t>2007-08-0206</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -30612,7 +30612,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>2007-08-206</t>
+          <t>2007-08-0206</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -30654,7 +30654,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>2007-08-206</t>
+          <t>2007-08-0206</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -30696,7 +30696,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>2007-08-206</t>
+          <t>2007-08-0206</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -30738,7 +30738,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>2007-08-207</t>
+          <t>2007-08-0207</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -30780,7 +30780,7 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>2007-08-207</t>
+          <t>2007-08-0207</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -30822,7 +30822,7 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>2007-08-207</t>
+          <t>2007-08-0207</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -30864,7 +30864,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>2007-08-208</t>
+          <t>2007-08-0208</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -30906,7 +30906,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>2007-08-208</t>
+          <t>2007-08-0208</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -30948,7 +30948,7 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>2007-08-208</t>
+          <t>2007-08-0208</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -30990,7 +30990,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>2007-08-208</t>
+          <t>2007-08-0208</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -31032,7 +31032,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>2007-08-208</t>
+          <t>2007-08-0208</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -31074,7 +31074,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>2007-08-208</t>
+          <t>2007-08-0208</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -31116,7 +31116,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>2007-08-208</t>
+          <t>2007-08-0208</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -31158,7 +31158,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>2007-08-208</t>
+          <t>2007-08-0208</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -31200,7 +31200,7 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>2007-08-208</t>
+          <t>2007-08-0208</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -31242,7 +31242,7 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>2007-08-208</t>
+          <t>2007-08-0208</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -31284,7 +31284,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>2007-08-208</t>
+          <t>2007-08-0208</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -31326,7 +31326,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>2007-08-209</t>
+          <t>2007-08-0209</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -31368,7 +31368,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>2007-08-209</t>
+          <t>2007-08-0209</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -31410,7 +31410,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>2007-08-209</t>
+          <t>2007-08-0209</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -31452,7 +31452,7 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>2007-08-209</t>
+          <t>2007-08-0209</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -31494,7 +31494,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>2007-08-209</t>
+          <t>2007-08-0209</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -31536,7 +31536,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>2007-08-209</t>
+          <t>2007-08-0209</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -31578,7 +31578,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>2007-08-209</t>
+          <t>2007-08-0209</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -31620,7 +31620,7 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>2007-08-210</t>
+          <t>2007-08-0210</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -31662,7 +31662,7 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>2007-08-210</t>
+          <t>2007-08-0210</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -31704,7 +31704,7 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>2007-08-210</t>
+          <t>2007-08-0210</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -31746,7 +31746,7 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>2007-08-210</t>
+          <t>2007-08-0210</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -31788,7 +31788,7 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>2007-08-210</t>
+          <t>2007-08-0210</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -31830,7 +31830,7 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>2007-08-210</t>
+          <t>2007-08-0210</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -31872,7 +31872,7 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>2007-08-210</t>
+          <t>2007-08-0210</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -31914,7 +31914,7 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>2007-08-211</t>
+          <t>2007-08-0211</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
@@ -31956,7 +31956,7 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>2007-08-211</t>
+          <t>2007-08-0211</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -31998,7 +31998,7 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>2007-08-211</t>
+          <t>2007-08-0211</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
@@ -32040,7 +32040,7 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>2007-08-211</t>
+          <t>2007-08-0211</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -32082,7 +32082,7 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>2007-08-211</t>
+          <t>2007-08-0211</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -32124,7 +32124,7 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>2007-08-211</t>
+          <t>2007-08-0211</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -32166,7 +32166,7 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>2007-08-211</t>
+          <t>2007-08-0211</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -32208,7 +32208,7 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>2007-08-212</t>
+          <t>2007-08-0212</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -32250,7 +32250,7 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>2007-08-212</t>
+          <t>2007-08-0212</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -32292,7 +32292,7 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>2007-08-212</t>
+          <t>2007-08-0212</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -32334,7 +32334,7 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>2007-08-212</t>
+          <t>2007-08-0212</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -32376,7 +32376,7 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>2007-08-212</t>
+          <t>2007-08-0212</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -32418,7 +32418,7 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>2007-08-212</t>
+          <t>2007-08-0212</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
@@ -32460,7 +32460,7 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>2007-08-213</t>
+          <t>2007-08-0213</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -32502,7 +32502,7 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>2007-08-213</t>
+          <t>2007-08-0213</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -32544,7 +32544,7 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>2007-08-213</t>
+          <t>2007-08-0213</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -32586,7 +32586,7 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>2007-08-213</t>
+          <t>2007-08-0213</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -32628,7 +32628,7 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>2007-08-213</t>
+          <t>2007-08-0213</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -32670,7 +32670,7 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>2007-08-213</t>
+          <t>2007-08-0213</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -32712,7 +32712,7 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>2007-08-213</t>
+          <t>2007-08-0213</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -32754,7 +32754,7 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>2007-08-213</t>
+          <t>2007-08-0213</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
@@ -32796,7 +32796,7 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>2007-08-213</t>
+          <t>2007-08-0213</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -32838,7 +32838,7 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>2007-08-213</t>
+          <t>2007-08-0213</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
@@ -32880,7 +32880,7 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>2007-08-213</t>
+          <t>2007-08-0213</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -32922,7 +32922,7 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>2007-08-213</t>
+          <t>2007-08-0213</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -32964,7 +32964,7 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>2007-08-213</t>
+          <t>2007-08-0213</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -33006,7 +33006,7 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>2007-08-213</t>
+          <t>2007-08-0213</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
@@ -33048,7 +33048,7 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>2007-08-214</t>
+          <t>2007-08-0214</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -33090,7 +33090,7 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>2007-08-214</t>
+          <t>2007-08-0214</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
@@ -33132,7 +33132,7 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>2007-08-219</t>
+          <t>2007-08-0219</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
@@ -33174,7 +33174,7 @@
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>2007-08-219</t>
+          <t>2007-08-0219</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
@@ -33216,7 +33216,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>2007-08-219</t>
+          <t>2007-08-0219</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>2007-08-219</t>
+          <t>2007-08-0219</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
@@ -33300,7 +33300,7 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>2007-08-219</t>
+          <t>2007-08-0219</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
@@ -33342,7 +33342,7 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>2007-08-219</t>
+          <t>2007-08-0219</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -33384,7 +33384,7 @@
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>2007-08-219</t>
+          <t>2007-08-0219</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -33426,7 +33426,7 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>2007-08-219</t>
+          <t>2007-08-0219</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
@@ -33468,7 +33468,7 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>2007-08-219</t>
+          <t>2007-08-0219</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
@@ -33510,7 +33510,7 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>2007-08-219</t>
+          <t>2007-08-0219</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
@@ -33552,7 +33552,7 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>2007-08-220</t>
+          <t>2007-08-0220</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
@@ -33594,7 +33594,7 @@
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>2007-08-220</t>
+          <t>2007-08-0220</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
@@ -33636,7 +33636,7 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>2007-08-220</t>
+          <t>2007-08-0220</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
@@ -33678,7 +33678,7 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>2007-08-220</t>
+          <t>2007-08-0220</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
@@ -33720,7 +33720,7 @@
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>2007-08-220</t>
+          <t>2007-08-0220</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
@@ -33762,7 +33762,7 @@
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>2007-08-220</t>
+          <t>2007-08-0220</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
@@ -33804,7 +33804,7 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>2007-08-220</t>
+          <t>2007-08-0220</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
@@ -33846,7 +33846,7 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>2007-08-220</t>
+          <t>2007-08-0220</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
@@ -33888,7 +33888,7 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>2007-08-220</t>
+          <t>2007-08-0220</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
@@ -33930,7 +33930,7 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>2007-08-220</t>
+          <t>2007-08-0220</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
@@ -33972,7 +33972,7 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>2007-08-221</t>
+          <t>2007-08-0221</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
@@ -34014,7 +34014,7 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>2007-08-221</t>
+          <t>2007-08-0221</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
@@ -34056,7 +34056,7 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>2007-08-221</t>
+          <t>2007-08-0221</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
@@ -34098,7 +34098,7 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>2007-08-222</t>
+          <t>2007-08-0222</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
@@ -34140,7 +34140,7 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>2007-08-222</t>
+          <t>2007-08-0222</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
@@ -34182,7 +34182,7 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>2007-08-222</t>
+          <t>2007-08-0222</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
@@ -34224,7 +34224,7 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>2007-08-222</t>
+          <t>2007-08-0222</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -34266,7 +34266,7 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>2007-08-222</t>
+          <t>2007-08-0222</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
@@ -34308,7 +34308,7 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>2007-08-222</t>
+          <t>2007-08-0222</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
@@ -34350,7 +34350,7 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>2007-08-222</t>
+          <t>2007-08-0222</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
@@ -34392,7 +34392,7 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>2007-08-222</t>
+          <t>2007-08-0222</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
@@ -34434,7 +34434,7 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>2007-08-222</t>
+          <t>2007-08-0222</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
@@ -34476,7 +34476,7 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>2007-08-222</t>
+          <t>2007-08-0222</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
@@ -34518,7 +34518,7 @@
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>2007-08-222</t>
+          <t>2007-08-0222</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
@@ -34560,7 +34560,7 @@
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>2007-08-222</t>
+          <t>2007-08-0222</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
@@ -34602,7 +34602,7 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>2007-08-222</t>
+          <t>2007-08-0222</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
@@ -34644,7 +34644,7 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>2007-08-223</t>
+          <t>2007-08-0223</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -34686,7 +34686,7 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>2007-08-223</t>
+          <t>2007-08-0223</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
@@ -34728,7 +34728,7 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>2007-08-223</t>
+          <t>2007-08-0223</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
@@ -34770,7 +34770,7 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>2007-08-223</t>
+          <t>2007-08-0223</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
@@ -34812,7 +34812,7 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>2007-08-223</t>
+          <t>2007-08-0223</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
@@ -34854,7 +34854,7 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>2007-08-223</t>
+          <t>2007-08-0223</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
@@ -34896,7 +34896,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>2007-08-223</t>
+          <t>2007-08-0223</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
@@ -34938,7 +34938,7 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>2007-08-224</t>
+          <t>2007-08-0224</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
@@ -34980,7 +34980,7 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>2007-08-224</t>
+          <t>2007-08-0224</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
@@ -35022,7 +35022,7 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>2007-08-224</t>
+          <t>2007-08-0224</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
@@ -35064,7 +35064,7 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>2007-08-224</t>
+          <t>2007-08-0224</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
@@ -35106,7 +35106,7 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>2007-08-224</t>
+          <t>2007-08-0224</t>
         </is>
       </c>
       <c r="C828" t="inlineStr">
@@ -35148,7 +35148,7 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>2007-08-224</t>
+          <t>2007-08-0224</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
@@ -35190,7 +35190,7 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>2007-08-224</t>
+          <t>2007-08-0224</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
@@ -35232,7 +35232,7 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>2007-08-224</t>
+          <t>2007-08-0224</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
@@ -35274,7 +35274,7 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>2007-08-225</t>
+          <t>2007-08-0225</t>
         </is>
       </c>
       <c r="C832" t="inlineStr">
@@ -35316,7 +35316,7 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>2007-08-225</t>
+          <t>2007-08-0225</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
@@ -35358,7 +35358,7 @@
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>2007-08-225</t>
+          <t>2007-08-0225</t>
         </is>
       </c>
       <c r="C834" t="inlineStr">
@@ -35400,7 +35400,7 @@
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>2007-08-225</t>
+          <t>2007-08-0225</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
@@ -35442,7 +35442,7 @@
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>2007-08-225</t>
+          <t>2007-08-0225</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
@@ -35484,7 +35484,7 @@
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>2007-08-225</t>
+          <t>2007-08-0225</t>
         </is>
       </c>
       <c r="C837" t="inlineStr">
@@ -35526,7 +35526,7 @@
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>2007-08-226</t>
+          <t>2007-08-0226</t>
         </is>
       </c>
       <c r="C838" t="inlineStr">
@@ -35568,7 +35568,7 @@
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>2007-08-226</t>
+          <t>2007-08-0226</t>
         </is>
       </c>
       <c r="C839" t="inlineStr">
@@ -35610,7 +35610,7 @@
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>2007-08-226</t>
+          <t>2007-08-0226</t>
         </is>
       </c>
       <c r="C840" t="inlineStr">
@@ -35652,7 +35652,7 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>2007-08-226</t>
+          <t>2007-08-0226</t>
         </is>
       </c>
       <c r="C841" t="inlineStr">
@@ -35694,7 +35694,7 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>2007-08-226</t>
+          <t>2007-08-0226</t>
         </is>
       </c>
       <c r="C842" t="inlineStr">
@@ -35736,7 +35736,7 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>2007-08-226</t>
+          <t>2007-08-0226</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
@@ -35778,7 +35778,7 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>2007-08-226</t>
+          <t>2007-08-0226</t>
         </is>
       </c>
       <c r="C844" t="inlineStr">
@@ -35820,7 +35820,7 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>2007-08-226</t>
+          <t>2007-08-0226</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
@@ -35862,7 +35862,7 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>2007-08-227</t>
+          <t>2007-08-0227</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
@@ -35904,7 +35904,7 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>2007-08-227</t>
+          <t>2007-08-0227</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
@@ -35946,7 +35946,7 @@
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>2007-08-227</t>
+          <t>2007-08-0227</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
@@ -35988,7 +35988,7 @@
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>2007-08-227</t>
+          <t>2007-08-0227</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
@@ -36030,7 +36030,7 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>2007-08-227</t>
+          <t>2007-08-0227</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
@@ -36072,7 +36072,7 @@
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>2007-08-227</t>
+          <t>2007-08-0227</t>
         </is>
       </c>
       <c r="C851" t="inlineStr">
@@ -36114,7 +36114,7 @@
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>2007-08-227</t>
+          <t>2007-08-0227</t>
         </is>
       </c>
       <c r="C852" t="inlineStr">
@@ -36156,7 +36156,7 @@
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>2007-08-227</t>
+          <t>2007-08-0227</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
@@ -36198,7 +36198,7 @@
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>2007-08-227</t>
+          <t>2007-08-0227</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
@@ -36240,7 +36240,7 @@
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>2007-08-227</t>
+          <t>2007-08-0227</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
@@ -36282,7 +36282,7 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>2007-08-228</t>
+          <t>2007-08-0228</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
@@ -36324,7 +36324,7 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>2007-08-228</t>
+          <t>2007-08-0228</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
@@ -36366,7 +36366,7 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>2007-08-228</t>
+          <t>2007-08-0228</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
@@ -36408,7 +36408,7 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>2007-08-229</t>
+          <t>2007-08-0229</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
@@ -36450,7 +36450,7 @@
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>2007-08-229</t>
+          <t>2007-08-0229</t>
         </is>
       </c>
       <c r="C860" t="inlineStr">
@@ -36492,7 +36492,7 @@
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>2007-08-229</t>
+          <t>2007-08-0229</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
@@ -36534,7 +36534,7 @@
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>2007-08-229</t>
+          <t>2007-08-0229</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
@@ -36576,7 +36576,7 @@
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>2007-08-229</t>
+          <t>2007-08-0229</t>
         </is>
       </c>
       <c r="C863" t="inlineStr">
@@ -36618,7 +36618,7 @@
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>2007-08-229</t>
+          <t>2007-08-0229</t>
         </is>
       </c>
       <c r="C864" t="inlineStr">
@@ -36660,7 +36660,7 @@
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>2007-08-229</t>
+          <t>2007-08-0229</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
@@ -36702,7 +36702,7 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>2007-08-229</t>
+          <t>2007-08-0229</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
@@ -36744,7 +36744,7 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>2007-08-229</t>
+          <t>2007-08-0229</t>
         </is>
       </c>
       <c r="C867" t="inlineStr">
@@ -36786,7 +36786,7 @@
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>2007-08-229</t>
+          <t>2007-08-0229</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
@@ -36828,7 +36828,7 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>2007-08-229</t>
+          <t>2007-08-0229</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
@@ -36870,7 +36870,7 @@
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>2007-08-229</t>
+          <t>2007-08-0229</t>
         </is>
       </c>
       <c r="C870" t="inlineStr">
@@ -36912,7 +36912,7 @@
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>2007-08-301</t>
+          <t>2007-08-0301</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
@@ -36954,7 +36954,7 @@
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>2007-08-301</t>
+          <t>2007-08-0301</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
@@ -36996,7 +36996,7 @@
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>2007-08-301</t>
+          <t>2007-08-0301</t>
         </is>
       </c>
       <c r="C873" t="inlineStr">
@@ -37038,7 +37038,7 @@
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>2007-08-301</t>
+          <t>2007-08-0301</t>
         </is>
       </c>
       <c r="C874" t="inlineStr">
@@ -37080,7 +37080,7 @@
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>2007-08-301</t>
+          <t>2007-08-0301</t>
         </is>
       </c>
       <c r="C875" t="inlineStr">
@@ -37122,7 +37122,7 @@
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>2007-08-302</t>
+          <t>2007-08-0302</t>
         </is>
       </c>
       <c r="C876" t="inlineStr">
@@ -37164,7 +37164,7 @@
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>2007-08-302</t>
+          <t>2007-08-0302</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
@@ -37206,7 +37206,7 @@
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>2007-08-302</t>
+          <t>2007-08-0302</t>
         </is>
       </c>
       <c r="C878" t="inlineStr">
@@ -37248,7 +37248,7 @@
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>2007-08-302</t>
+          <t>2007-08-0302</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
@@ -37290,7 +37290,7 @@
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>2007-08-302</t>
+          <t>2007-08-0302</t>
         </is>
       </c>
       <c r="C880" t="inlineStr">
@@ -37332,7 +37332,7 @@
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>2007-08-302</t>
+          <t>2007-08-0302</t>
         </is>
       </c>
       <c r="C881" t="inlineStr">
@@ -37374,7 +37374,7 @@
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>2007-08-302</t>
+          <t>2007-08-0302</t>
         </is>
       </c>
       <c r="C882" t="inlineStr">
@@ -37416,7 +37416,7 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>2007-08-302</t>
+          <t>2007-08-0302</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
@@ -37458,7 +37458,7 @@
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>2007-08-302</t>
+          <t>2007-08-0302</t>
         </is>
       </c>
       <c r="C884" t="inlineStr">
@@ -37500,7 +37500,7 @@
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>2007-08-302</t>
+          <t>2007-08-0302</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
@@ -37542,7 +37542,7 @@
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>2007-08-302</t>
+          <t>2007-08-0302</t>
         </is>
       </c>
       <c r="C886" t="inlineStr">
@@ -37584,7 +37584,7 @@
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>2007-08-303</t>
+          <t>2007-08-0303</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
@@ -37626,7 +37626,7 @@
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>2007-08-303</t>
+          <t>2007-08-0303</t>
         </is>
       </c>
       <c r="C888" t="inlineStr">
@@ -37668,7 +37668,7 @@
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>2007-08-303</t>
+          <t>2007-08-0303</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
@@ -37710,7 +37710,7 @@
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>2007-08-304</t>
+          <t>2007-08-0304</t>
         </is>
       </c>
       <c r="C890" t="inlineStr">
@@ -37752,7 +37752,7 @@
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>2007-08-304</t>
+          <t>2007-08-0304</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
@@ -37794,7 +37794,7 @@
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>2007-08-304</t>
+          <t>2007-08-0304</t>
         </is>
       </c>
       <c r="C892" t="inlineStr">
@@ -37836,7 +37836,7 @@
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>2007-08-304</t>
+          <t>2007-08-0304</t>
         </is>
       </c>
       <c r="C893" t="inlineStr">
@@ -37878,7 +37878,7 @@
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>2007-08-304</t>
+          <t>2007-08-0304</t>
         </is>
       </c>
       <c r="C894" t="inlineStr">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>2007-08-304</t>
+          <t>2007-08-0304</t>
         </is>
       </c>
       <c r="C895" t="inlineStr">
@@ -37962,7 +37962,7 @@
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>2007-08-304</t>
+          <t>2007-08-0304</t>
         </is>
       </c>
       <c r="C896" t="inlineStr">
@@ -38004,7 +38004,7 @@
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>2007-08-304</t>
+          <t>2007-08-0304</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
@@ -38046,7 +38046,7 @@
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>2007-08-305</t>
+          <t>2007-08-0305</t>
         </is>
       </c>
       <c r="C898" t="inlineStr">
@@ -38088,7 +38088,7 @@
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>2007-08-305</t>
+          <t>2007-08-0305</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
@@ -38130,7 +38130,7 @@
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>2007-08-305</t>
+          <t>2007-08-0305</t>
         </is>
       </c>
       <c r="C900" t="inlineStr">
@@ -38172,7 +38172,7 @@
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>2007-08-305</t>
+          <t>2007-08-0305</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
@@ -38214,7 +38214,7 @@
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>2007-08-305</t>
+          <t>2007-08-0305</t>
         </is>
       </c>
       <c r="C902" t="inlineStr">
@@ -38256,7 +38256,7 @@
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>2007-08-305</t>
+          <t>2007-08-0305</t>
         </is>
       </c>
       <c r="C903" t="inlineStr">
@@ -38298,7 +38298,7 @@
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>2007-08-305</t>
+          <t>2007-08-0305</t>
         </is>
       </c>
       <c r="C904" t="inlineStr">
@@ -38340,7 +38340,7 @@
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>2007-08-305</t>
+          <t>2007-08-0305</t>
         </is>
       </c>
       <c r="C905" t="inlineStr">
@@ -38382,7 +38382,7 @@
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>2007-08-305</t>
+          <t>2007-08-0305</t>
         </is>
       </c>
       <c r="C906" t="inlineStr">
@@ -38424,7 +38424,7 @@
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>2007-08-305</t>
+          <t>2007-08-0305</t>
         </is>
       </c>
       <c r="C907" t="inlineStr">
@@ -38466,7 +38466,7 @@
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>2007-08-305</t>
+          <t>2007-08-0305</t>
         </is>
       </c>
       <c r="C908" t="inlineStr">
@@ -38508,7 +38508,7 @@
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>2007-08-305</t>
+          <t>2007-08-0305</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
@@ -38550,7 +38550,7 @@
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t>2007-08-306</t>
+          <t>2007-08-0306</t>
         </is>
       </c>
       <c r="C910" t="inlineStr">
@@ -38592,7 +38592,7 @@
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>2007-08-306</t>
+          <t>2007-08-0306</t>
         </is>
       </c>
       <c r="C911" t="inlineStr">
@@ -38634,7 +38634,7 @@
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>2007-08-306</t>
+          <t>2007-08-0306</t>
         </is>
       </c>
       <c r="C912" t="inlineStr">
@@ -38676,7 +38676,7 @@
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>2007-08-307</t>
+          <t>2007-08-0307</t>
         </is>
       </c>
       <c r="C913" t="inlineStr">
@@ -38718,7 +38718,7 @@
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t>2007-08-307</t>
+          <t>2007-08-0307</t>
         </is>
       </c>
       <c r="C914" t="inlineStr">
@@ -38760,7 +38760,7 @@
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>2007-08-307</t>
+          <t>2007-08-0307</t>
         </is>
       </c>
       <c r="C915" t="inlineStr">
@@ -38802,7 +38802,7 @@
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>2007-08-307</t>
+          <t>2007-08-0307</t>
         </is>
       </c>
       <c r="C916" t="inlineStr">
@@ -38844,7 +38844,7 @@
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>2007-08-307</t>
+          <t>2007-08-0307</t>
         </is>
       </c>
       <c r="C917" t="inlineStr">
@@ -38886,7 +38886,7 @@
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>2007-08-307</t>
+          <t>2007-08-0307</t>
         </is>
       </c>
       <c r="C918" t="inlineStr">
@@ -38928,7 +38928,7 @@
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>2007-08-307</t>
+          <t>2007-08-0307</t>
         </is>
       </c>
       <c r="C919" t="inlineStr">
@@ -38970,7 +38970,7 @@
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>2007-08-307</t>
+          <t>2007-08-0307</t>
         </is>
       </c>
       <c r="C920" t="inlineStr">
@@ -39012,7 +39012,7 @@
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>2007-08-307</t>
+          <t>2007-08-0307</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
@@ -39054,7 +39054,7 @@
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>2007-08-307</t>
+          <t>2007-08-0307</t>
         </is>
       </c>
       <c r="C922" t="inlineStr">
@@ -39096,7 +39096,7 @@
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>2007-08-307</t>
+          <t>2007-08-0307</t>
         </is>
       </c>
       <c r="C923" t="inlineStr">
@@ -39138,7 +39138,7 @@
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>2007-08-307</t>
+          <t>2007-08-0307</t>
         </is>
       </c>
       <c r="C924" t="inlineStr">
@@ -39180,7 +39180,7 @@
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>2007-08-308</t>
+          <t>2007-08-0308</t>
         </is>
       </c>
       <c r="C925" t="inlineStr">
@@ -39222,7 +39222,7 @@
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>2007-08-308</t>
+          <t>2007-08-0308</t>
         </is>
       </c>
       <c r="C926" t="inlineStr">
@@ -39264,7 +39264,7 @@
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>2007-08-308</t>
+          <t>2007-08-0308</t>
         </is>
       </c>
       <c r="C927" t="inlineStr">
@@ -39306,7 +39306,7 @@
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>2007-08-308</t>
+          <t>2007-08-0308</t>
         </is>
       </c>
       <c r="C928" t="inlineStr">
@@ -39348,7 +39348,7 @@
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>2007-08-308</t>
+          <t>2007-08-0308</t>
         </is>
       </c>
       <c r="C929" t="inlineStr">
@@ -39390,7 +39390,7 @@
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>2007-08-308</t>
+          <t>2007-08-0308</t>
         </is>
       </c>
       <c r="C930" t="inlineStr">
@@ -39432,7 +39432,7 @@
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>2007-08-308</t>
+          <t>2007-08-0308</t>
         </is>
       </c>
       <c r="C931" t="inlineStr">
@@ -39474,7 +39474,7 @@
       </c>
       <c r="B932" t="inlineStr">
         <is>
-          <t>2007-08-308</t>
+          <t>2007-08-0308</t>
         </is>
       </c>
       <c r="C932" t="inlineStr">
@@ -39516,7 +39516,7 @@
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>2007-08-308</t>
+          <t>2007-08-0308</t>
         </is>
       </c>
       <c r="C933" t="inlineStr">
@@ -39558,7 +39558,7 @@
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>2007-08-308</t>
+          <t>2007-08-0308</t>
         </is>
       </c>
       <c r="C934" t="inlineStr">
@@ -39600,7 +39600,7 @@
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>2007-08-309</t>
+          <t>2007-08-0309</t>
         </is>
       </c>
       <c r="C935" t="inlineStr">
@@ -39642,7 +39642,7 @@
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>2007-08-309</t>
+          <t>2007-08-0309</t>
         </is>
       </c>
       <c r="C936" t="inlineStr">
@@ -39684,7 +39684,7 @@
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>2007-08-309</t>
+          <t>2007-08-0309</t>
         </is>
       </c>
       <c r="C937" t="inlineStr">
@@ -39726,7 +39726,7 @@
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>2007-08-309</t>
+          <t>2007-08-0309</t>
         </is>
       </c>
       <c r="C938" t="inlineStr">
@@ -39768,7 +39768,7 @@
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>2007-08-309</t>
+          <t>2007-08-0309</t>
         </is>
       </c>
       <c r="C939" t="inlineStr">
@@ -39810,7 +39810,7 @@
       </c>
       <c r="B940" t="inlineStr">
         <is>
-          <t>2007-08-310</t>
+          <t>2007-08-0310</t>
         </is>
       </c>
       <c r="C940" t="inlineStr">
@@ -39852,7 +39852,7 @@
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>2007-08-310</t>
+          <t>2007-08-0310</t>
         </is>
       </c>
       <c r="C941" t="inlineStr">
@@ -39894,7 +39894,7 @@
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t>2007-08-310</t>
+          <t>2007-08-0310</t>
         </is>
       </c>
       <c r="C942" t="inlineStr">
@@ -39936,7 +39936,7 @@
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>2007-08-310</t>
+          <t>2007-08-0310</t>
         </is>
       </c>
       <c r="C943" t="inlineStr">
@@ -39978,7 +39978,7 @@
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>2007-08-310</t>
+          <t>2007-08-0310</t>
         </is>
       </c>
       <c r="C944" t="inlineStr">
@@ -40020,7 +40020,7 @@
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>2007-08-310</t>
+          <t>2007-08-0310</t>
         </is>
       </c>
       <c r="C945" t="inlineStr">
@@ -40062,7 +40062,7 @@
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>2007-08-310</t>
+          <t>2007-08-0310</t>
         </is>
       </c>
       <c r="C946" t="inlineStr">
@@ -40104,7 +40104,7 @@
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>2007-08-311</t>
+          <t>2007-08-0311</t>
         </is>
       </c>
       <c r="C947" t="inlineStr">
@@ -40146,7 +40146,7 @@
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t>2007-08-311</t>
+          <t>2007-08-0311</t>
         </is>
       </c>
       <c r="C948" t="inlineStr">
@@ -40188,7 +40188,7 @@
       </c>
       <c r="B949" t="inlineStr">
         <is>
-          <t>2007-08-311</t>
+          <t>2007-08-0311</t>
         </is>
       </c>
       <c r="C949" t="inlineStr">
@@ -40230,7 +40230,7 @@
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t>2007-08-311</t>
+          <t>2007-08-0311</t>
         </is>
       </c>
       <c r="C950" t="inlineStr">
@@ -40272,7 +40272,7 @@
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t>2007-08-311</t>
+          <t>2007-08-0311</t>
         </is>
       </c>
       <c r="C951" t="inlineStr">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="B952" t="inlineStr">
         <is>
-          <t>2007-08-311</t>
+          <t>2007-08-0311</t>
         </is>
       </c>
       <c r="C952" t="inlineStr">
@@ -40356,7 +40356,7 @@
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>2007-08-312</t>
+          <t>2007-08-0312</t>
         </is>
       </c>
       <c r="C953" t="inlineStr">
@@ -40398,7 +40398,7 @@
       </c>
       <c r="B954" t="inlineStr">
         <is>
-          <t>2007-08-312</t>
+          <t>2007-08-0312</t>
         </is>
       </c>
       <c r="C954" t="inlineStr">
@@ -40440,7 +40440,7 @@
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>2007-08-312</t>
+          <t>2007-08-0312</t>
         </is>
       </c>
       <c r="C955" t="inlineStr">
@@ -40482,7 +40482,7 @@
       </c>
       <c r="B956" t="inlineStr">
         <is>
-          <t>2007-08-312</t>
+          <t>2007-08-0312</t>
         </is>
       </c>
       <c r="C956" t="inlineStr">
@@ -40524,7 +40524,7 @@
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>2007-08-312</t>
+          <t>2007-08-0312</t>
         </is>
       </c>
       <c r="C957" t="inlineStr">
@@ -40566,7 +40566,7 @@
       </c>
       <c r="B958" t="inlineStr">
         <is>
-          <t>2007-08-312</t>
+          <t>2007-08-0312</t>
         </is>
       </c>
       <c r="C958" t="inlineStr">
@@ -40608,7 +40608,7 @@
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>2007-08-312</t>
+          <t>2007-08-0312</t>
         </is>
       </c>
       <c r="C959" t="inlineStr">
@@ -40650,7 +40650,7 @@
       </c>
       <c r="B960" t="inlineStr">
         <is>
-          <t>2007-08-312</t>
+          <t>2007-08-0312</t>
         </is>
       </c>
       <c r="C960" t="inlineStr">
@@ -40692,7 +40692,7 @@
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>2007-08-312</t>
+          <t>2007-08-0312</t>
         </is>
       </c>
       <c r="C961" t="inlineStr">
@@ -40734,7 +40734,7 @@
       </c>
       <c r="B962" t="inlineStr">
         <is>
-          <t>2007-08-312</t>
+          <t>2007-08-0312</t>
         </is>
       </c>
       <c r="C962" t="inlineStr">
@@ -40776,7 +40776,7 @@
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>2007-08-312</t>
+          <t>2007-08-0312</t>
         </is>
       </c>
       <c r="C963" t="inlineStr">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="B964" t="inlineStr">
         <is>
-          <t>2007-08-313</t>
+          <t>2007-08-0313</t>
         </is>
       </c>
       <c r="C964" t="inlineStr">
@@ -40860,7 +40860,7 @@
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>2007-08-313</t>
+          <t>2007-08-0313</t>
         </is>
       </c>
       <c r="C965" t="inlineStr">
@@ -40902,7 +40902,7 @@
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t>2007-08-313</t>
+          <t>2007-08-0313</t>
         </is>
       </c>
       <c r="C966" t="inlineStr">
@@ -40944,7 +40944,7 @@
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>2007-08-314</t>
+          <t>2007-08-0314</t>
         </is>
       </c>
       <c r="C967" t="inlineStr">
@@ -40986,7 +40986,7 @@
       </c>
       <c r="B968" t="inlineStr">
         <is>
-          <t>2007-08-314</t>
+          <t>2007-08-0314</t>
         </is>
       </c>
       <c r="C968" t="inlineStr">
@@ -41028,7 +41028,7 @@
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>2007-08-314</t>
+          <t>2007-08-0314</t>
         </is>
       </c>
       <c r="C969" t="inlineStr">
@@ -41070,7 +41070,7 @@
       </c>
       <c r="B970" t="inlineStr">
         <is>
-          <t>2007-08-314</t>
+          <t>2007-08-0314</t>
         </is>
       </c>
       <c r="C970" t="inlineStr">
@@ -41112,7 +41112,7 @@
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t>2007-08-314</t>
+          <t>2007-08-0314</t>
         </is>
       </c>
       <c r="C971" t="inlineStr">
@@ -41154,7 +41154,7 @@
       </c>
       <c r="B972" t="inlineStr">
         <is>
-          <t>2007-08-314</t>
+          <t>2007-08-0314</t>
         </is>
       </c>
       <c r="C972" t="inlineStr">
@@ -41196,7 +41196,7 @@
       </c>
       <c r="B973" t="inlineStr">
         <is>
-          <t>2007-08-314</t>
+          <t>2007-08-0314</t>
         </is>
       </c>
       <c r="C973" t="inlineStr">
@@ -41238,7 +41238,7 @@
       </c>
       <c r="B974" t="inlineStr">
         <is>
-          <t>2007-08-314</t>
+          <t>2007-08-0314</t>
         </is>
       </c>
       <c r="C974" t="inlineStr">
@@ -41280,7 +41280,7 @@
       </c>
       <c r="B975" t="inlineStr">
         <is>
-          <t>2007-08-314</t>
+          <t>2007-08-0314</t>
         </is>
       </c>
       <c r="C975" t="inlineStr">
@@ -41322,7 +41322,7 @@
       </c>
       <c r="B976" t="inlineStr">
         <is>
-          <t>2007-08-314</t>
+          <t>2007-08-0314</t>
         </is>
       </c>
       <c r="C976" t="inlineStr">
@@ -41364,7 +41364,7 @@
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t>2007-08-315</t>
+          <t>2007-08-0315</t>
         </is>
       </c>
       <c r="C977" t="inlineStr">
@@ -41406,7 +41406,7 @@
       </c>
       <c r="B978" t="inlineStr">
         <is>
-          <t>2007-08-315</t>
+          <t>2007-08-0315</t>
         </is>
       </c>
       <c r="C978" t="inlineStr">
@@ -41448,7 +41448,7 @@
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>2007-08-315</t>
+          <t>2007-08-0315</t>
         </is>
       </c>
       <c r="C979" t="inlineStr">
@@ -41490,7 +41490,7 @@
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t>2007-08-315</t>
+          <t>2007-08-0315</t>
         </is>
       </c>
       <c r="C980" t="inlineStr">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>2007-08-315</t>
+          <t>2007-08-0315</t>
         </is>
       </c>
       <c r="C981" t="inlineStr">
@@ -41574,7 +41574,7 @@
       </c>
       <c r="B982" t="inlineStr">
         <is>
-          <t>2007-08-315</t>
+          <t>2007-08-0315</t>
         </is>
       </c>
       <c r="C982" t="inlineStr">
@@ -41616,7 +41616,7 @@
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>2007-08-315</t>
+          <t>2007-08-0315</t>
         </is>
       </c>
       <c r="C983" t="inlineStr">
@@ -41658,7 +41658,7 @@
       </c>
       <c r="B984" t="inlineStr">
         <is>
-          <t>2007-08-315</t>
+          <t>2007-08-0315</t>
         </is>
       </c>
       <c r="C984" t="inlineStr">
@@ -41700,7 +41700,7 @@
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t>2007-08-316</t>
+          <t>2007-08-0316</t>
         </is>
       </c>
       <c r="C985" t="inlineStr">
@@ -41742,7 +41742,7 @@
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t>2007-08-316</t>
+          <t>2007-08-0316</t>
         </is>
       </c>
       <c r="C986" t="inlineStr">
@@ -41784,7 +41784,7 @@
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>2007-08-316</t>
+          <t>2007-08-0316</t>
         </is>
       </c>
       <c r="C987" t="inlineStr">
@@ -41826,7 +41826,7 @@
       </c>
       <c r="B988" t="inlineStr">
         <is>
-          <t>2007-08-316</t>
+          <t>2007-08-0316</t>
         </is>
       </c>
       <c r="C988" t="inlineStr">
@@ -41868,7 +41868,7 @@
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>2007-08-316</t>
+          <t>2007-08-0316</t>
         </is>
       </c>
       <c r="C989" t="inlineStr">
@@ -41912,7 +41912,7 @@
       </c>
       <c r="B990" t="inlineStr">
         <is>
-          <t>2007-08-316</t>
+          <t>2007-08-0316</t>
         </is>
       </c>
       <c r="C990" t="inlineStr">
@@ -41954,7 +41954,7 @@
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>2007-08-316</t>
+          <t>2007-08-0316</t>
         </is>
       </c>
       <c r="C991" t="inlineStr">
@@ -41996,7 +41996,7 @@
       </c>
       <c r="B992" t="inlineStr">
         <is>
-          <t>2007-08-317</t>
+          <t>2007-08-0317</t>
         </is>
       </c>
       <c r="C992" t="inlineStr">
@@ -42038,7 +42038,7 @@
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t>2007-08-317</t>
+          <t>2007-08-0317</t>
         </is>
       </c>
       <c r="C993" t="inlineStr">
@@ -42080,7 +42080,7 @@
       </c>
       <c r="B994" t="inlineStr">
         <is>
-          <t>2007-08-317</t>
+          <t>2007-08-0317</t>
         </is>
       </c>
       <c r="C994" t="inlineStr">
@@ -42122,7 +42122,7 @@
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>2007-08-317</t>
+          <t>2007-08-0317</t>
         </is>
       </c>
       <c r="C995" t="inlineStr">
@@ -42164,7 +42164,7 @@
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t>2007-08-317</t>
+          <t>2007-08-0317</t>
         </is>
       </c>
       <c r="C996" t="inlineStr">
@@ -42206,7 +42206,7 @@
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>2007-08-317</t>
+          <t>2007-08-0317</t>
         </is>
       </c>
       <c r="C997" t="inlineStr">
@@ -42248,7 +42248,7 @@
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t>2007-08-317</t>
+          <t>2007-08-0317</t>
         </is>
       </c>
       <c r="C998" t="inlineStr">
@@ -42290,7 +42290,7 @@
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>2007-08-317</t>
+          <t>2007-08-0317</t>
         </is>
       </c>
       <c r="C999" t="inlineStr">
@@ -42332,7 +42332,7 @@
       </c>
       <c r="B1000" t="inlineStr">
         <is>
-          <t>2007-08-318</t>
+          <t>2007-08-0318</t>
         </is>
       </c>
       <c r="C1000" t="inlineStr">
@@ -42374,7 +42374,7 @@
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t>2007-08-318</t>
+          <t>2007-08-0318</t>
         </is>
       </c>
       <c r="C1001" t="inlineStr">
@@ -42416,7 +42416,7 @@
       </c>
       <c r="B1002" t="inlineStr">
         <is>
-          <t>2007-08-318</t>
+          <t>2007-08-0318</t>
         </is>
       </c>
       <c r="C1002" t="inlineStr">
@@ -42458,7 +42458,7 @@
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t>2007-08-318</t>
+          <t>2007-08-0318</t>
         </is>
       </c>
       <c r="C1003" t="inlineStr">
@@ -42500,7 +42500,7 @@
       </c>
       <c r="B1004" t="inlineStr">
         <is>
-          <t>2007-08-318</t>
+          <t>2007-08-0318</t>
         </is>
       </c>
       <c r="C1004" t="inlineStr">
@@ -42542,7 +42542,7 @@
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>2007-08-318</t>
+          <t>2007-08-0318</t>
         </is>
       </c>
       <c r="C1005" t="inlineStr">
@@ -42584,7 +42584,7 @@
       </c>
       <c r="B1006" t="inlineStr">
         <is>
-          <t>2007-08-318</t>
+          <t>2007-08-0318</t>
         </is>
       </c>
       <c r="C1006" t="inlineStr">
@@ -42626,7 +42626,7 @@
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>2007-08-319</t>
+          <t>2007-08-0319</t>
         </is>
       </c>
       <c r="C1007" t="inlineStr">
@@ -42668,7 +42668,7 @@
       </c>
       <c r="B1008" t="inlineStr">
         <is>
-          <t>2007-08-319</t>
+          <t>2007-08-0319</t>
         </is>
       </c>
       <c r="C1008" t="inlineStr">
@@ -42710,7 +42710,7 @@
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t>2007-08-319</t>
+          <t>2007-08-0319</t>
         </is>
       </c>
       <c r="C1009" t="inlineStr">
@@ -42752,7 +42752,7 @@
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t>2007-08-319</t>
+          <t>2007-08-0319</t>
         </is>
       </c>
       <c r="C1010" t="inlineStr">
@@ -42794,7 +42794,7 @@
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t>2007-08-319</t>
+          <t>2007-08-0319</t>
         </is>
       </c>
       <c r="C1011" t="inlineStr">
@@ -42836,7 +42836,7 @@
       </c>
       <c r="B1012" t="inlineStr">
         <is>
-          <t>2007-08-319</t>
+          <t>2007-08-0319</t>
         </is>
       </c>
       <c r="C1012" t="inlineStr">
@@ -42878,7 +42878,7 @@
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t>2007-08-319</t>
+          <t>2007-08-0319</t>
         </is>
       </c>
       <c r="C1013" t="inlineStr">
@@ -42920,7 +42920,7 @@
       </c>
       <c r="B1014" t="inlineStr">
         <is>
-          <t>2007-08-319</t>
+          <t>2007-08-0319</t>
         </is>
       </c>
       <c r="C1014" t="inlineStr">
@@ -42962,7 +42962,7 @@
       </c>
       <c r="B1015" t="inlineStr">
         <is>
-          <t>2007-08-319</t>
+          <t>2007-08-0319</t>
         </is>
       </c>
       <c r="C1015" t="inlineStr">
@@ -43004,7 +43004,7 @@
       </c>
       <c r="B1016" t="inlineStr">
         <is>
-          <t>2007-08-319</t>
+          <t>2007-08-0319</t>
         </is>
       </c>
       <c r="C1016" t="inlineStr">
@@ -43046,7 +43046,7 @@
       </c>
       <c r="B1017" t="inlineStr">
         <is>
-          <t>2007-08-320</t>
+          <t>2007-08-0320</t>
         </is>
       </c>
       <c r="C1017" t="inlineStr">
@@ -43088,7 +43088,7 @@
       </c>
       <c r="B1018" t="inlineStr">
         <is>
-          <t>2007-08-320</t>
+          <t>2007-08-0320</t>
         </is>
       </c>
       <c r="C1018" t="inlineStr">
@@ -43130,7 +43130,7 @@
       </c>
       <c r="B1019" t="inlineStr">
         <is>
-          <t>2007-08-320</t>
+          <t>2007-08-0320</t>
         </is>
       </c>
       <c r="C1019" t="inlineStr">
@@ -43172,7 +43172,7 @@
       </c>
       <c r="B1020" t="inlineStr">
         <is>
-          <t>2007-08-321</t>
+          <t>2007-08-0321</t>
         </is>
       </c>
       <c r="C1020" t="inlineStr">
@@ -43214,7 +43214,7 @@
       </c>
       <c r="B1021" t="inlineStr">
         <is>
-          <t>2007-08-321</t>
+          <t>2007-08-0321</t>
         </is>
       </c>
       <c r="C1021" t="inlineStr">
@@ -43256,7 +43256,7 @@
       </c>
       <c r="B1022" t="inlineStr">
         <is>
-          <t>2007-08-321</t>
+          <t>2007-08-0321</t>
         </is>
       </c>
       <c r="C1022" t="inlineStr">
@@ -43298,7 +43298,7 @@
       </c>
       <c r="B1023" t="inlineStr">
         <is>
-          <t>2007-08-321</t>
+          <t>2007-08-0321</t>
         </is>
       </c>
       <c r="C1023" t="inlineStr">
@@ -43340,7 +43340,7 @@
       </c>
       <c r="B1024" t="inlineStr">
         <is>
-          <t>2007-08-321</t>
+          <t>2007-08-0321</t>
         </is>
       </c>
       <c r="C1024" t="inlineStr">
@@ -43382,7 +43382,7 @@
       </c>
       <c r="B1025" t="inlineStr">
         <is>
-          <t>2007-08-321</t>
+          <t>2007-08-0321</t>
         </is>
       </c>
       <c r="C1025" t="inlineStr">
@@ -43424,7 +43424,7 @@
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t>2007-08-321</t>
+          <t>2007-08-0321</t>
         </is>
       </c>
       <c r="C1026" t="inlineStr">
@@ -43466,7 +43466,7 @@
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t>2007-08-321</t>
+          <t>2007-08-0321</t>
         </is>
       </c>
       <c r="C1027" t="inlineStr">
@@ -43508,7 +43508,7 @@
       </c>
       <c r="B1028" t="inlineStr">
         <is>
-          <t>2007-08-321</t>
+          <t>2007-08-0321</t>
         </is>
       </c>
       <c r="C1028" t="inlineStr">
@@ -43550,7 +43550,7 @@
       </c>
       <c r="B1029" t="inlineStr">
         <is>
-          <t>2007-08-321</t>
+          <t>2007-08-0321</t>
         </is>
       </c>
       <c r="C1029" t="inlineStr">
@@ -43592,7 +43592,7 @@
       </c>
       <c r="B1030" t="inlineStr">
         <is>
-          <t>2007-08-322</t>
+          <t>2007-08-0322</t>
         </is>
       </c>
       <c r="C1030" t="inlineStr">
@@ -43634,7 +43634,7 @@
       </c>
       <c r="B1031" t="inlineStr">
         <is>
-          <t>2007-08-322</t>
+          <t>2007-08-0322</t>
         </is>
       </c>
       <c r="C1031" t="inlineStr">
@@ -43676,7 +43676,7 @@
       </c>
       <c r="B1032" t="inlineStr">
         <is>
-          <t>2007-08-322</t>
+          <t>2007-08-0322</t>
         </is>
       </c>
       <c r="C1032" t="inlineStr">
@@ -43718,7 +43718,7 @@
       </c>
       <c r="B1033" t="inlineStr">
         <is>
-          <t>2007-08-322</t>
+          <t>2007-08-0322</t>
         </is>
       </c>
       <c r="C1033" t="inlineStr">
@@ -43760,7 +43760,7 @@
       </c>
       <c r="B1034" t="inlineStr">
         <is>
-          <t>2007-08-322</t>
+          <t>2007-08-0322</t>
         </is>
       </c>
       <c r="C1034" t="inlineStr">
@@ -43802,7 +43802,7 @@
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t>2007-08-322</t>
+          <t>2007-08-0322</t>
         </is>
       </c>
       <c r="C1035" t="inlineStr">
@@ -43844,7 +43844,7 @@
       </c>
       <c r="B1036" t="inlineStr">
         <is>
-          <t>2007-08-322</t>
+          <t>2007-08-0322</t>
         </is>
       </c>
       <c r="C1036" t="inlineStr">
@@ -43886,7 +43886,7 @@
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t>2007-08-322</t>
+          <t>2007-08-0322</t>
         </is>
       </c>
       <c r="C1037" t="inlineStr">
@@ -43928,7 +43928,7 @@
       </c>
       <c r="B1038" t="inlineStr">
         <is>
-          <t>2007-08-322</t>
+          <t>2007-08-0322</t>
         </is>
       </c>
       <c r="C1038" t="inlineStr">
@@ -43970,7 +43970,7 @@
       </c>
       <c r="B1039" t="inlineStr">
         <is>
-          <t>2007-08-322</t>
+          <t>2007-08-0322</t>
         </is>
       </c>
       <c r="C1039" t="inlineStr">
@@ -44012,7 +44012,7 @@
       </c>
       <c r="B1040" t="inlineStr">
         <is>
-          <t>2007-08-322</t>
+          <t>2007-08-0322</t>
         </is>
       </c>
       <c r="C1040" t="inlineStr">
@@ -44054,7 +44054,7 @@
       </c>
       <c r="B1041" t="inlineStr">
         <is>
-          <t>2007-08-323</t>
+          <t>2007-08-0323</t>
         </is>
       </c>
       <c r="C1041" t="inlineStr">
@@ -44096,7 +44096,7 @@
       </c>
       <c r="B1042" t="inlineStr">
         <is>
-          <t>2007-08-323</t>
+          <t>2007-08-0323</t>
         </is>
       </c>
       <c r="C1042" t="inlineStr">
@@ -44138,7 +44138,7 @@
       </c>
       <c r="B1043" t="inlineStr">
         <is>
-          <t>2007-08-323</t>
+          <t>2007-08-0323</t>
         </is>
       </c>
       <c r="C1043" t="inlineStr">
@@ -44180,7 +44180,7 @@
       </c>
       <c r="B1044" t="inlineStr">
         <is>
-          <t>2007-08-323</t>
+          <t>2007-08-0323</t>
         </is>
       </c>
       <c r="C1044" t="inlineStr">
@@ -44222,7 +44222,7 @@
       </c>
       <c r="B1045" t="inlineStr">
         <is>
-          <t>2007-08-324</t>
+          <t>2007-08-0324</t>
         </is>
       </c>
       <c r="C1045" t="inlineStr">
@@ -44264,7 +44264,7 @@
       </c>
       <c r="B1046" t="inlineStr">
         <is>
-          <t>2007-08-324</t>
+          <t>2007-08-0324</t>
         </is>
       </c>
       <c r="C1046" t="inlineStr">
@@ -44306,7 +44306,7 @@
       </c>
       <c r="B1047" t="inlineStr">
         <is>
-          <t>2007-08-324</t>
+          <t>2007-08-0324</t>
         </is>
       </c>
       <c r="C1047" t="inlineStr">
@@ -44348,7 +44348,7 @@
       </c>
       <c r="B1048" t="inlineStr">
         <is>
-          <t>2007-08-324</t>
+          <t>2007-08-0324</t>
         </is>
       </c>
       <c r="C1048" t="inlineStr">
@@ -44390,7 +44390,7 @@
       </c>
       <c r="B1049" t="inlineStr">
         <is>
-          <t>2007-08-324</t>
+          <t>2007-08-0324</t>
         </is>
       </c>
       <c r="C1049" t="inlineStr">
@@ -44432,7 +44432,7 @@
       </c>
       <c r="B1050" t="inlineStr">
         <is>
-          <t>2007-08-324</t>
+          <t>2007-08-0324</t>
         </is>
       </c>
       <c r="C1050" t="inlineStr">
@@ -44474,7 +44474,7 @@
       </c>
       <c r="B1051" t="inlineStr">
         <is>
-          <t>2007-08-324</t>
+          <t>2007-08-0324</t>
         </is>
       </c>
       <c r="C1051" t="inlineStr">
@@ -44516,7 +44516,7 @@
       </c>
       <c r="B1052" t="inlineStr">
         <is>
-          <t>2007-08-324</t>
+          <t>2007-08-0324</t>
         </is>
       </c>
       <c r="C1052" t="inlineStr">
@@ -44558,7 +44558,7 @@
       </c>
       <c r="B1053" t="inlineStr">
         <is>
-          <t>2007-08-325</t>
+          <t>2007-08-0325</t>
         </is>
       </c>
       <c r="C1053" t="inlineStr">
@@ -44600,7 +44600,7 @@
       </c>
       <c r="B1054" t="inlineStr">
         <is>
-          <t>2007-08-325</t>
+          <t>2007-08-0325</t>
         </is>
       </c>
       <c r="C1054" t="inlineStr">
@@ -44642,7 +44642,7 @@
       </c>
       <c r="B1055" t="inlineStr">
         <is>
-          <t>2007-08-325</t>
+          <t>2007-08-0325</t>
         </is>
       </c>
       <c r="C1055" t="inlineStr">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="B1056" t="inlineStr">
         <is>
-          <t>2007-08-325</t>
+          <t>2007-08-0325</t>
         </is>
       </c>
       <c r="C1056" t="inlineStr">
@@ -44726,7 +44726,7 @@
       </c>
       <c r="B1057" t="inlineStr">
         <is>
-          <t>2007-08-325</t>
+          <t>2007-08-0325</t>
         </is>
       </c>
       <c r="C1057" t="inlineStr">
@@ -44768,7 +44768,7 @@
       </c>
       <c r="B1058" t="inlineStr">
         <is>
-          <t>2007-08-325</t>
+          <t>2007-08-0325</t>
         </is>
       </c>
       <c r="C1058" t="inlineStr">
@@ -44810,7 +44810,7 @@
       </c>
       <c r="B1059" t="inlineStr">
         <is>
-          <t>2007-08-326</t>
+          <t>2007-08-0326</t>
         </is>
       </c>
       <c r="C1059" t="inlineStr">
@@ -44852,7 +44852,7 @@
       </c>
       <c r="B1060" t="inlineStr">
         <is>
-          <t>2007-08-326</t>
+          <t>2007-08-0326</t>
         </is>
       </c>
       <c r="C1060" t="inlineStr">
@@ -44894,7 +44894,7 @@
       </c>
       <c r="B1061" t="inlineStr">
         <is>
-          <t>2007-08-326</t>
+          <t>2007-08-0326</t>
         </is>
       </c>
       <c r="C1061" t="inlineStr">
@@ -44936,7 +44936,7 @@
       </c>
       <c r="B1062" t="inlineStr">
         <is>
-          <t>2007-08-326</t>
+          <t>2007-08-0326</t>
         </is>
       </c>
       <c r="C1062" t="inlineStr">
@@ -44978,7 +44978,7 @@
       </c>
       <c r="B1063" t="inlineStr">
         <is>
-          <t>2007-08-326</t>
+          <t>2007-08-0326</t>
         </is>
       </c>
       <c r="C1063" t="inlineStr">
@@ -45020,7 +45020,7 @@
       </c>
       <c r="B1064" t="inlineStr">
         <is>
-          <t>2007-08-326</t>
+          <t>2007-08-0326</t>
         </is>
       </c>
       <c r="C1064" t="inlineStr">
@@ -45062,7 +45062,7 @@
       </c>
       <c r="B1065" t="inlineStr">
         <is>
-          <t>2007-08-326</t>
+          <t>2007-08-0326</t>
         </is>
       </c>
       <c r="C1065" t="inlineStr">
@@ -45104,7 +45104,7 @@
       </c>
       <c r="B1066" t="inlineStr">
         <is>
-          <t>2007-08-326</t>
+          <t>2007-08-0326</t>
         </is>
       </c>
       <c r="C1066" t="inlineStr">
@@ -45146,7 +45146,7 @@
       </c>
       <c r="B1067" t="inlineStr">
         <is>
-          <t>2007-08-326</t>
+          <t>2007-08-0326</t>
         </is>
       </c>
       <c r="C1067" t="inlineStr">
@@ -45188,7 +45188,7 @@
       </c>
       <c r="B1068" t="inlineStr">
         <is>
-          <t>2007-08-326</t>
+          <t>2007-08-0326</t>
         </is>
       </c>
       <c r="C1068" t="inlineStr">
@@ -45230,7 +45230,7 @@
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t>2007-08-326</t>
+          <t>2007-08-0326</t>
         </is>
       </c>
       <c r="C1069" t="inlineStr">
@@ -45272,7 +45272,7 @@
       </c>
       <c r="B1070" t="inlineStr">
         <is>
-          <t>2007-08-326</t>
+          <t>2007-08-0326</t>
         </is>
       </c>
       <c r="C1070" t="inlineStr">
@@ -45314,7 +45314,7 @@
       </c>
       <c r="B1071" t="inlineStr">
         <is>
-          <t>2007-08-327</t>
+          <t>2007-08-0327</t>
         </is>
       </c>
       <c r="C1071" t="inlineStr">
@@ -45356,7 +45356,7 @@
       </c>
       <c r="B1072" t="inlineStr">
         <is>
-          <t>2007-08-327</t>
+          <t>2007-08-0327</t>
         </is>
       </c>
       <c r="C1072" t="inlineStr">
@@ -45398,7 +45398,7 @@
       </c>
       <c r="B1073" t="inlineStr">
         <is>
-          <t>2007-08-327</t>
+          <t>2007-08-0327</t>
         </is>
       </c>
       <c r="C1073" t="inlineStr">
@@ -45440,7 +45440,7 @@
       </c>
       <c r="B1074" t="inlineStr">
         <is>
-          <t>2007-08-328</t>
+          <t>2007-08-0328</t>
         </is>
       </c>
       <c r="C1074" t="inlineStr">
@@ -45482,7 +45482,7 @@
       </c>
       <c r="B1075" t="inlineStr">
         <is>
-          <t>2007-08-328</t>
+          <t>2007-08-0328</t>
         </is>
       </c>
       <c r="C1075" t="inlineStr">
@@ -45524,7 +45524,7 @@
       </c>
       <c r="B1076" t="inlineStr">
         <is>
-          <t>2007-08-328</t>
+          <t>2007-08-0328</t>
         </is>
       </c>
       <c r="C1076" t="inlineStr">
@@ -45566,7 +45566,7 @@
       </c>
       <c r="B1077" t="inlineStr">
         <is>
-          <t>2007-08-328</t>
+          <t>2007-08-0328</t>
         </is>
       </c>
       <c r="C1077" t="inlineStr">
@@ -45608,7 +45608,7 @@
       </c>
       <c r="B1078" t="inlineStr">
         <is>
-          <t>2007-08-328</t>
+          <t>2007-08-0328</t>
         </is>
       </c>
       <c r="C1078" t="inlineStr">
@@ -45650,7 +45650,7 @@
       </c>
       <c r="B1079" t="inlineStr">
         <is>
-          <t>2007-08-328</t>
+          <t>2007-08-0328</t>
         </is>
       </c>
       <c r="C1079" t="inlineStr">
@@ -45692,7 +45692,7 @@
       </c>
       <c r="B1080" t="inlineStr">
         <is>
-          <t>2007-08-328</t>
+          <t>2007-08-0328</t>
         </is>
       </c>
       <c r="C1080" t="inlineStr">
@@ -45734,7 +45734,7 @@
       </c>
       <c r="B1081" t="inlineStr">
         <is>
-          <t>2007-08-328</t>
+          <t>2007-08-0328</t>
         </is>
       </c>
       <c r="C1081" t="inlineStr">
@@ -45776,7 +45776,7 @@
       </c>
       <c r="B1082" t="inlineStr">
         <is>
-          <t>2007-08-328</t>
+          <t>2007-08-0328</t>
         </is>
       </c>
       <c r="C1082" t="inlineStr">
@@ -45818,7 +45818,7 @@
       </c>
       <c r="B1083" t="inlineStr">
         <is>
-          <t>2007-08-328</t>
+          <t>2007-08-0328</t>
         </is>
       </c>
       <c r="C1083" t="inlineStr">
@@ -45860,7 +45860,7 @@
       </c>
       <c r="B1084" t="inlineStr">
         <is>
-          <t>2007-08-328</t>
+          <t>2007-08-0328</t>
         </is>
       </c>
       <c r="C1084" t="inlineStr">
@@ -45902,7 +45902,7 @@
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t>2007-08-329</t>
+          <t>2007-08-0329</t>
         </is>
       </c>
       <c r="C1085" t="inlineStr">
@@ -45944,7 +45944,7 @@
       </c>
       <c r="B1086" t="inlineStr">
         <is>
-          <t>2007-08-329</t>
+          <t>2007-08-0329</t>
         </is>
       </c>
       <c r="C1086" t="inlineStr">
@@ -45986,7 +45986,7 @@
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t>2007-08-329</t>
+          <t>2007-08-0329</t>
         </is>
       </c>
       <c r="C1087" t="inlineStr">
@@ -46028,7 +46028,7 @@
       </c>
       <c r="B1088" t="inlineStr">
         <is>
-          <t>2007-08-329</t>
+          <t>2007-08-0329</t>
         </is>
       </c>
       <c r="C1088" t="inlineStr">
@@ -46070,7 +46070,7 @@
       </c>
       <c r="B1089" t="inlineStr">
         <is>
-          <t>2007-08-329</t>
+          <t>2007-08-0329</t>
         </is>
       </c>
       <c r="C1089" t="inlineStr">
@@ -46112,7 +46112,7 @@
       </c>
       <c r="B1090" t="inlineStr">
         <is>
-          <t>2007-08-329</t>
+          <t>2007-08-0329</t>
         </is>
       </c>
       <c r="C1090" t="inlineStr">
@@ -46154,7 +46154,7 @@
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t>2007-08-330</t>
+          <t>2007-08-0330</t>
         </is>
       </c>
       <c r="C1091" t="inlineStr">
@@ -46196,7 +46196,7 @@
       </c>
       <c r="B1092" t="inlineStr">
         <is>
-          <t>2007-08-330</t>
+          <t>2007-08-0330</t>
         </is>
       </c>
       <c r="C1092" t="inlineStr">
@@ -46238,7 +46238,7 @@
       </c>
       <c r="B1093" t="inlineStr">
         <is>
-          <t>2007-08-330</t>
+          <t>2007-08-0330</t>
         </is>
       </c>
       <c r="C1093" t="inlineStr">
@@ -46280,7 +46280,7 @@
       </c>
       <c r="B1094" t="inlineStr">
         <is>
-          <t>2007-08-330</t>
+          <t>2007-08-0330</t>
         </is>
       </c>
       <c r="C1094" t="inlineStr">
@@ -46322,7 +46322,7 @@
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t>2007-08-330</t>
+          <t>2007-08-0330</t>
         </is>
       </c>
       <c r="C1095" t="inlineStr">
@@ -46364,7 +46364,7 @@
       </c>
       <c r="B1096" t="inlineStr">
         <is>
-          <t>2007-08-330</t>
+          <t>2007-08-0330</t>
         </is>
       </c>
       <c r="C1096" t="inlineStr">
@@ -46406,7 +46406,7 @@
       </c>
       <c r="B1097" t="inlineStr">
         <is>
-          <t>2007-08-330</t>
+          <t>2007-08-0330</t>
         </is>
       </c>
       <c r="C1097" t="inlineStr">
@@ -46448,7 +46448,7 @@
       </c>
       <c r="B1098" t="inlineStr">
         <is>
-          <t>2007-08-330</t>
+          <t>2007-08-0330</t>
         </is>
       </c>
       <c r="C1098" t="inlineStr">
@@ -46490,7 +46490,7 @@
       </c>
       <c r="B1099" t="inlineStr">
         <is>
-          <t>2007-08-330</t>
+          <t>2007-08-0330</t>
         </is>
       </c>
       <c r="C1099" t="inlineStr">
@@ -46532,7 +46532,7 @@
       </c>
       <c r="B1100" t="inlineStr">
         <is>
-          <t>2007-08-331</t>
+          <t>2007-08-0331</t>
         </is>
       </c>
       <c r="C1100" t="inlineStr">
@@ -46574,7 +46574,7 @@
       </c>
       <c r="B1101" t="inlineStr">
         <is>
-          <t>2007-08-331</t>
+          <t>2007-08-0331</t>
         </is>
       </c>
       <c r="C1101" t="inlineStr">
@@ -46616,7 +46616,7 @@
       </c>
       <c r="B1102" t="inlineStr">
         <is>
-          <t>2007-08-331</t>
+          <t>2007-08-0331</t>
         </is>
       </c>
       <c r="C1102" t="inlineStr">
@@ -46658,7 +46658,7 @@
       </c>
       <c r="B1103" t="inlineStr">
         <is>
-          <t>2007-08-331</t>
+          <t>2007-08-0331</t>
         </is>
       </c>
       <c r="C1103" t="inlineStr">
@@ -46700,7 +46700,7 @@
       </c>
       <c r="B1104" t="inlineStr">
         <is>
-          <t>2007-08-331</t>
+          <t>2007-08-0331</t>
         </is>
       </c>
       <c r="C1104" t="inlineStr">
@@ -46742,7 +46742,7 @@
       </c>
       <c r="B1105" t="inlineStr">
         <is>
-          <t>2007-08-331</t>
+          <t>2007-08-0331</t>
         </is>
       </c>
       <c r="C1105" t="inlineStr">
@@ -46784,7 +46784,7 @@
       </c>
       <c r="B1106" t="inlineStr">
         <is>
-          <t>2007-08-401</t>
+          <t>2007-08-0401</t>
         </is>
       </c>
       <c r="C1106" t="inlineStr">
@@ -46826,7 +46826,7 @@
       </c>
       <c r="B1107" t="inlineStr">
         <is>
-          <t>2007-08-401</t>
+          <t>2007-08-0401</t>
         </is>
       </c>
       <c r="C1107" t="inlineStr">
@@ -46868,7 +46868,7 @@
       </c>
       <c r="B1108" t="inlineStr">
         <is>
-          <t>2007-08-401</t>
+          <t>2007-08-0401</t>
         </is>
       </c>
       <c r="C1108" t="inlineStr">
@@ -46910,7 +46910,7 @@
       </c>
       <c r="B1109" t="inlineStr">
         <is>
-          <t>2007-08-401</t>
+          <t>2007-08-0401</t>
         </is>
       </c>
       <c r="C1109" t="inlineStr">
@@ -46952,7 +46952,7 @@
       </c>
       <c r="B1110" t="inlineStr">
         <is>
-          <t>2007-08-401</t>
+          <t>2007-08-0401</t>
         </is>
       </c>
       <c r="C1110" t="inlineStr">
@@ -46994,7 +46994,7 @@
       </c>
       <c r="B1111" t="inlineStr">
         <is>
-          <t>2007-08-401</t>
+          <t>2007-08-0401</t>
         </is>
       </c>
       <c r="C1111" t="inlineStr">
@@ -47036,7 +47036,7 @@
       </c>
       <c r="B1112" t="inlineStr">
         <is>
-          <t>2007-08-401</t>
+          <t>2007-08-0401</t>
         </is>
       </c>
       <c r="C1112" t="inlineStr">
@@ -47078,7 +47078,7 @@
       </c>
       <c r="B1113" t="inlineStr">
         <is>
-          <t>2007-08-401</t>
+          <t>2007-08-0401</t>
         </is>
       </c>
       <c r="C1113" t="inlineStr">
@@ -47120,7 +47120,7 @@
       </c>
       <c r="B1114" t="inlineStr">
         <is>
-          <t>2007-08-402</t>
+          <t>2007-08-0402</t>
         </is>
       </c>
       <c r="C1114" t="inlineStr">
@@ -47162,7 +47162,7 @@
       </c>
       <c r="B1115" t="inlineStr">
         <is>
-          <t>2007-08-402</t>
+          <t>2007-08-0402</t>
         </is>
       </c>
       <c r="C1115" t="inlineStr">
@@ -47204,7 +47204,7 @@
       </c>
       <c r="B1116" t="inlineStr">
         <is>
-          <t>2007-08-402</t>
+          <t>2007-08-0402</t>
         </is>
       </c>
       <c r="C1116" t="inlineStr">
@@ -47246,7 +47246,7 @@
       </c>
       <c r="B1117" t="inlineStr">
         <is>
-          <t>2007-08-402</t>
+          <t>2007-08-0402</t>
         </is>
       </c>
       <c r="C1117" t="inlineStr">
@@ -47288,7 +47288,7 @@
       </c>
       <c r="B1118" t="inlineStr">
         <is>
-          <t>2007-08-402</t>
+          <t>2007-08-0402</t>
         </is>
       </c>
       <c r="C1118" t="inlineStr">
@@ -47330,7 +47330,7 @@
       </c>
       <c r="B1119" t="inlineStr">
         <is>
-          <t>2007-08-402</t>
+          <t>2007-08-0402</t>
         </is>
       </c>
       <c r="C1119" t="inlineStr">
@@ -47372,7 +47372,7 @@
       </c>
       <c r="B1120" t="inlineStr">
         <is>
-          <t>2007-08-402</t>
+          <t>2007-08-0402</t>
         </is>
       </c>
       <c r="C1120" t="inlineStr">
@@ -47414,7 +47414,7 @@
       </c>
       <c r="B1121" t="inlineStr">
         <is>
-          <t>2007-08-402</t>
+          <t>2007-08-0402</t>
         </is>
       </c>
       <c r="C1121" t="inlineStr">
@@ -47456,7 +47456,7 @@
       </c>
       <c r="B1122" t="inlineStr">
         <is>
-          <t>2007-08-402</t>
+          <t>2007-08-0402</t>
         </is>
       </c>
       <c r="C1122" t="inlineStr">
@@ -47498,7 +47498,7 @@
       </c>
       <c r="B1123" t="inlineStr">
         <is>
-          <t>2007-08-402</t>
+          <t>2007-08-0402</t>
         </is>
       </c>
       <c r="C1123" t="inlineStr">
@@ -47540,7 +47540,7 @@
       </c>
       <c r="B1124" t="inlineStr">
         <is>
-          <t>2007-08-403</t>
+          <t>2007-08-0403</t>
         </is>
       </c>
       <c r="C1124" t="inlineStr">
@@ -47582,7 +47582,7 @@
       </c>
       <c r="B1125" t="inlineStr">
         <is>
-          <t>2007-08-403</t>
+          <t>2007-08-0403</t>
         </is>
       </c>
       <c r="C1125" t="inlineStr">
@@ -47624,7 +47624,7 @@
       </c>
       <c r="B1126" t="inlineStr">
         <is>
-          <t>2007-08-403</t>
+          <t>2007-08-0403</t>
         </is>
       </c>
       <c r="C1126" t="inlineStr">
@@ -47666,7 +47666,7 @@
       </c>
       <c r="B1127" t="inlineStr">
         <is>
-          <t>2007-08-404</t>
+          <t>2007-08-0404</t>
         </is>
       </c>
       <c r="C1127" t="inlineStr">
@@ -47708,7 +47708,7 @@
       </c>
       <c r="B1128" t="inlineStr">
         <is>
-          <t>2007-08-404</t>
+          <t>2007-08-0404</t>
         </is>
       </c>
       <c r="C1128" t="inlineStr">
@@ -47750,7 +47750,7 @@
       </c>
       <c r="B1129" t="inlineStr">
         <is>
-          <t>2007-08-404</t>
+          <t>2007-08-0404</t>
         </is>
       </c>
       <c r="C1129" t="inlineStr">
@@ -47792,7 +47792,7 @@
       </c>
       <c r="B1130" t="inlineStr">
         <is>
-          <t>2007-08-404</t>
+          <t>2007-08-0404</t>
         </is>
       </c>
       <c r="C1130" t="inlineStr">
@@ -47834,7 +47834,7 @@
       </c>
       <c r="B1131" t="inlineStr">
         <is>
-          <t>2007-08-404</t>
+          <t>2007-08-0404</t>
         </is>
       </c>
       <c r="C1131" t="inlineStr">
@@ -47876,7 +47876,7 @@
       </c>
       <c r="B1132" t="inlineStr">
         <is>
-          <t>2007-08-404</t>
+          <t>2007-08-0404</t>
         </is>
       </c>
       <c r="C1132" t="inlineStr">
@@ -47918,7 +47918,7 @@
       </c>
       <c r="B1133" t="inlineStr">
         <is>
-          <t>2007-08-404</t>
+          <t>2007-08-0404</t>
         </is>
       </c>
       <c r="C1133" t="inlineStr">
@@ -47960,7 +47960,7 @@
       </c>
       <c r="B1134" t="inlineStr">
         <is>
-          <t>2007-08-404</t>
+          <t>2007-08-0404</t>
         </is>
       </c>
       <c r="C1134" t="inlineStr">
@@ -48002,7 +48002,7 @@
       </c>
       <c r="B1135" t="inlineStr">
         <is>
-          <t>2007-08-404</t>
+          <t>2007-08-0404</t>
         </is>
       </c>
       <c r="C1135" t="inlineStr">
@@ -48044,7 +48044,7 @@
       </c>
       <c r="B1136" t="inlineStr">
         <is>
-          <t>2007-08-404</t>
+          <t>2007-08-0404</t>
         </is>
       </c>
       <c r="C1136" t="inlineStr">
@@ -48086,7 +48086,7 @@
       </c>
       <c r="B1137" t="inlineStr">
         <is>
-          <t>2007-08-404</t>
+          <t>2007-08-0404</t>
         </is>
       </c>
       <c r="C1137" t="inlineStr">
@@ -48128,7 +48128,7 @@
       </c>
       <c r="B1138" t="inlineStr">
         <is>
-          <t>2007-08-405</t>
+          <t>2007-08-0405</t>
         </is>
       </c>
       <c r="C1138" t="inlineStr">
@@ -48170,7 +48170,7 @@
       </c>
       <c r="B1139" t="inlineStr">
         <is>
-          <t>2007-08-405</t>
+          <t>2007-08-0405</t>
         </is>
       </c>
       <c r="C1139" t="inlineStr">
@@ -48212,7 +48212,7 @@
       </c>
       <c r="B1140" t="inlineStr">
         <is>
-          <t>2007-08-405</t>
+          <t>2007-08-0405</t>
         </is>
       </c>
       <c r="C1140" t="inlineStr">
@@ -48254,7 +48254,7 @@
       </c>
       <c r="B1141" t="inlineStr">
         <is>
-          <t>2007-08-405</t>
+          <t>2007-08-0405</t>
         </is>
       </c>
       <c r="C1141" t="inlineStr">
@@ -48296,7 +48296,7 @@
       </c>
       <c r="B1142" t="inlineStr">
         <is>
-          <t>2007-08-405</t>
+          <t>2007-08-0405</t>
         </is>
       </c>
       <c r="C1142" t="inlineStr">
@@ -48338,7 +48338,7 @@
       </c>
       <c r="B1143" t="inlineStr">
         <is>
-          <t>2007-08-405</t>
+          <t>2007-08-0405</t>
         </is>
       </c>
       <c r="C1143" t="inlineStr">
@@ -48380,7 +48380,7 @@
       </c>
       <c r="B1144" t="inlineStr">
         <is>
-          <t>2007-08-406</t>
+          <t>2007-08-0406</t>
         </is>
       </c>
       <c r="C1144" t="inlineStr">
@@ -48422,7 +48422,7 @@
       </c>
       <c r="B1145" t="inlineStr">
         <is>
-          <t>2007-08-406</t>
+          <t>2007-08-0406</t>
         </is>
       </c>
       <c r="C1145" t="inlineStr">
@@ -48464,7 +48464,7 @@
       </c>
       <c r="B1146" t="inlineStr">
         <is>
-          <t>2007-08-406</t>
+          <t>2007-08-0406</t>
         </is>
       </c>
       <c r="C1146" t="inlineStr">
@@ -48506,7 +48506,7 @@
       </c>
       <c r="B1147" t="inlineStr">
         <is>
-          <t>2007-08-406</t>
+          <t>2007-08-0406</t>
         </is>
       </c>
       <c r="C1147" t="inlineStr">
@@ -48548,7 +48548,7 @@
       </c>
       <c r="B1148" t="inlineStr">
         <is>
-          <t>2007-08-406</t>
+          <t>2007-08-0406</t>
         </is>
       </c>
       <c r="C1148" t="inlineStr">
@@ -48590,7 +48590,7 @@
       </c>
       <c r="B1149" t="inlineStr">
         <is>
-          <t>2007-08-406</t>
+          <t>2007-08-0406</t>
         </is>
       </c>
       <c r="C1149" t="inlineStr">
@@ -48632,7 +48632,7 @@
       </c>
       <c r="B1150" t="inlineStr">
         <is>
-          <t>2007-08-406</t>
+          <t>2007-08-0406</t>
         </is>
       </c>
       <c r="C1150" t="inlineStr">
@@ -48674,7 +48674,7 @@
       </c>
       <c r="B1151" t="inlineStr">
         <is>
-          <t>2007-08-406</t>
+          <t>2007-08-0406</t>
         </is>
       </c>
       <c r="C1151" t="inlineStr">
@@ -48716,7 +48716,7 @@
       </c>
       <c r="B1152" t="inlineStr">
         <is>
-          <t>2007-08-406</t>
+          <t>2007-08-0406</t>
         </is>
       </c>
       <c r="C1152" t="inlineStr">
@@ -48758,7 +48758,7 @@
       </c>
       <c r="B1153" t="inlineStr">
         <is>
-          <t>2007-08-406</t>
+          <t>2007-08-0406</t>
         </is>
       </c>
       <c r="C1153" t="inlineStr">
@@ -48800,7 +48800,7 @@
       </c>
       <c r="B1154" t="inlineStr">
         <is>
-          <t>2007-08-408</t>
+          <t>2007-08-0408</t>
         </is>
       </c>
       <c r="C1154" t="inlineStr">
@@ -48842,7 +48842,7 @@
       </c>
       <c r="B1155" t="inlineStr">
         <is>
-          <t>2007-08-408</t>
+          <t>2007-08-0408</t>
         </is>
       </c>
       <c r="C1155" t="inlineStr">
@@ -48884,7 +48884,7 @@
       </c>
       <c r="B1156" t="inlineStr">
         <is>
-          <t>2007-08-408</t>
+          <t>2007-08-0408</t>
         </is>
       </c>
       <c r="C1156" t="inlineStr">
@@ -48926,7 +48926,7 @@
       </c>
       <c r="B1157" t="inlineStr">
         <is>
-          <t>2007-08-408</t>
+          <t>2007-08-0408</t>
         </is>
       </c>
       <c r="C1157" t="inlineStr">
@@ -48968,7 +48968,7 @@
       </c>
       <c r="B1158" t="inlineStr">
         <is>
-          <t>2007-08-408</t>
+          <t>2007-08-0408</t>
         </is>
       </c>
       <c r="C1158" t="inlineStr">
@@ -49010,7 +49010,7 @@
       </c>
       <c r="B1159" t="inlineStr">
         <is>
-          <t>2007-08-408</t>
+          <t>2007-08-0408</t>
         </is>
       </c>
       <c r="C1159" t="inlineStr">
@@ -49052,7 +49052,7 @@
       </c>
       <c r="B1160" t="inlineStr">
         <is>
-          <t>2007-08-408</t>
+          <t>2007-08-0408</t>
         </is>
       </c>
       <c r="C1160" t="inlineStr">
@@ -49094,7 +49094,7 @@
       </c>
       <c r="B1161" t="inlineStr">
         <is>
-          <t>2007-08-408</t>
+          <t>2007-08-0408</t>
         </is>
       </c>
       <c r="C1161" t="inlineStr">
@@ -49136,7 +49136,7 @@
       </c>
       <c r="B1162" t="inlineStr">
         <is>
-          <t>2007-08-408</t>
+          <t>2007-08-0408</t>
         </is>
       </c>
       <c r="C1162" t="inlineStr">
@@ -49178,7 +49178,7 @@
       </c>
       <c r="B1163" t="inlineStr">
         <is>
-          <t>2007-08-408</t>
+          <t>2007-08-0408</t>
         </is>
       </c>
       <c r="C1163" t="inlineStr">
@@ -49220,7 +49220,7 @@
       </c>
       <c r="B1164" t="inlineStr">
         <is>
-          <t>2007-08-408</t>
+          <t>2007-08-0408</t>
         </is>
       </c>
       <c r="C1164" t="inlineStr">
@@ -49262,7 +49262,7 @@
       </c>
       <c r="B1165" t="inlineStr">
         <is>
-          <t>2007-08-409</t>
+          <t>2007-08-0409</t>
         </is>
       </c>
       <c r="C1165" t="inlineStr">
@@ -49304,7 +49304,7 @@
       </c>
       <c r="B1166" t="inlineStr">
         <is>
-          <t>2007-08-409</t>
+          <t>2007-08-0409</t>
         </is>
       </c>
       <c r="C1166" t="inlineStr">
@@ -49346,7 +49346,7 @@
       </c>
       <c r="B1167" t="inlineStr">
         <is>
-          <t>2007-08-409</t>
+          <t>2007-08-0409</t>
         </is>
       </c>
       <c r="C1167" t="inlineStr">
@@ -49388,7 +49388,7 @@
       </c>
       <c r="B1168" t="inlineStr">
         <is>
-          <t>2007-08-409</t>
+          <t>2007-08-0409</t>
         </is>
       </c>
       <c r="C1168" t="inlineStr">
@@ -49430,7 +49430,7 @@
       </c>
       <c r="B1169" t="inlineStr">
         <is>
-          <t>2007-08-409</t>
+          <t>2007-08-0409</t>
         </is>
       </c>
       <c r="C1169" t="inlineStr">
@@ -49472,7 +49472,7 @@
       </c>
       <c r="B1170" t="inlineStr">
         <is>
-          <t>2007-08-409</t>
+          <t>2007-08-0409</t>
         </is>
       </c>
       <c r="C1170" t="inlineStr">
@@ -49514,7 +49514,7 @@
       </c>
       <c r="B1171" t="inlineStr">
         <is>
-          <t>2007-08-409</t>
+          <t>2007-08-0409</t>
         </is>
       </c>
       <c r="C1171" t="inlineStr">
@@ -49556,7 +49556,7 @@
       </c>
       <c r="B1172" t="inlineStr">
         <is>
-          <t>2007-08-409</t>
+          <t>2007-08-0409</t>
         </is>
       </c>
       <c r="C1172" t="inlineStr">
@@ -49598,7 +49598,7 @@
       </c>
       <c r="B1173" t="inlineStr">
         <is>
-          <t>2007-08-409</t>
+          <t>2007-08-0409</t>
         </is>
       </c>
       <c r="C1173" t="inlineStr">
@@ -49640,7 +49640,7 @@
       </c>
       <c r="B1174" t="inlineStr">
         <is>
-          <t>2007-08-410</t>
+          <t>2007-08-0410</t>
         </is>
       </c>
       <c r="C1174" t="inlineStr">
@@ -49682,7 +49682,7 @@
       </c>
       <c r="B1175" t="inlineStr">
         <is>
-          <t>2007-08-410</t>
+          <t>2007-08-0410</t>
         </is>
       </c>
       <c r="C1175" t="inlineStr">
@@ -49724,7 +49724,7 @@
       </c>
       <c r="B1176" t="inlineStr">
         <is>
-          <t>2007-08-410</t>
+          <t>2007-08-0410</t>
         </is>
       </c>
       <c r="C1176" t="inlineStr">
@@ -49766,7 +49766,7 @@
       </c>
       <c r="B1177" t="inlineStr">
         <is>
-          <t>2007-08-411</t>
+          <t>2007-08-0411</t>
         </is>
       </c>
       <c r="C1177" t="inlineStr">
@@ -49808,7 +49808,7 @@
       </c>
       <c r="B1178" t="inlineStr">
         <is>
-          <t>2007-08-411</t>
+          <t>2007-08-0411</t>
         </is>
       </c>
       <c r="C1178" t="inlineStr">
@@ -49850,7 +49850,7 @@
       </c>
       <c r="B1179" t="inlineStr">
         <is>
-          <t>2007-08-411</t>
+          <t>2007-08-0411</t>
         </is>
       </c>
       <c r="C1179" t="inlineStr">
@@ -49892,7 +49892,7 @@
       </c>
       <c r="B1180" t="inlineStr">
         <is>
-          <t>2007-08-411</t>
+          <t>2007-08-0411</t>
         </is>
       </c>
       <c r="C1180" t="inlineStr">
@@ -49934,7 +49934,7 @@
       </c>
       <c r="B1181" t="inlineStr">
         <is>
-          <t>2007-08-411</t>
+          <t>2007-08-0411</t>
         </is>
       </c>
       <c r="C1181" t="inlineStr">
@@ -49976,7 +49976,7 @@
       </c>
       <c r="B1182" t="inlineStr">
         <is>
-          <t>2007-08-411</t>
+          <t>2007-08-0411</t>
         </is>
       </c>
       <c r="C1182" t="inlineStr">
@@ -50018,7 +50018,7 @@
       </c>
       <c r="B1183" t="inlineStr">
         <is>
-          <t>2007-08-411</t>
+          <t>2007-08-0411</t>
         </is>
       </c>
       <c r="C1183" t="inlineStr">
@@ -50060,7 +50060,7 @@
       </c>
       <c r="B1184" t="inlineStr">
         <is>
-          <t>2007-08-411</t>
+          <t>2007-08-0411</t>
         </is>
       </c>
       <c r="C1184" t="inlineStr">
@@ -50102,7 +50102,7 @@
       </c>
       <c r="B1185" t="inlineStr">
         <is>
-          <t>2007-08-411</t>
+          <t>2007-08-0411</t>
         </is>
       </c>
       <c r="C1185" t="inlineStr">
@@ -50144,7 +50144,7 @@
       </c>
       <c r="B1186" t="inlineStr">
         <is>
-          <t>2007-08-411</t>
+          <t>2007-08-0411</t>
         </is>
       </c>
       <c r="C1186" t="inlineStr">
@@ -50186,7 +50186,7 @@
       </c>
       <c r="B1187" t="inlineStr">
         <is>
-          <t>2007-08-411</t>
+          <t>2007-08-0411</t>
         </is>
       </c>
       <c r="C1187" t="inlineStr">
@@ -50228,7 +50228,7 @@
       </c>
       <c r="B1188" t="inlineStr">
         <is>
-          <t>2007-08-411</t>
+          <t>2007-08-0411</t>
         </is>
       </c>
       <c r="C1188" t="inlineStr">
@@ -50270,7 +50270,7 @@
       </c>
       <c r="B1189" t="inlineStr">
         <is>
-          <t>2007-08-412</t>
+          <t>2007-08-0412</t>
         </is>
       </c>
       <c r="C1189" t="inlineStr">
@@ -50312,7 +50312,7 @@
       </c>
       <c r="B1190" t="inlineStr">
         <is>
-          <t>2007-08-412</t>
+          <t>2007-08-0412</t>
         </is>
       </c>
       <c r="C1190" t="inlineStr">
@@ -50354,7 +50354,7 @@
       </c>
       <c r="B1191" t="inlineStr">
         <is>
-          <t>2007-08-412</t>
+          <t>2007-08-0412</t>
         </is>
       </c>
       <c r="C1191" t="inlineStr">
@@ -50396,7 +50396,7 @@
       </c>
       <c r="B1192" t="inlineStr">
         <is>
-          <t>2007-08-412</t>
+          <t>2007-08-0412</t>
         </is>
       </c>
       <c r="C1192" t="inlineStr">
@@ -50438,7 +50438,7 @@
       </c>
       <c r="B1193" t="inlineStr">
         <is>
-          <t>2007-08-412</t>
+          <t>2007-08-0412</t>
         </is>
       </c>
       <c r="C1193" t="inlineStr">
@@ -50480,7 +50480,7 @@
       </c>
       <c r="B1194" t="inlineStr">
         <is>
-          <t>2007-08-412</t>
+          <t>2007-08-0412</t>
         </is>
       </c>
       <c r="C1194" t="inlineStr">
@@ -50522,7 +50522,7 @@
       </c>
       <c r="B1195" t="inlineStr">
         <is>
-          <t>2007-08-412</t>
+          <t>2007-08-0412</t>
         </is>
       </c>
       <c r="C1195" t="inlineStr">
@@ -50564,7 +50564,7 @@
       </c>
       <c r="B1196" t="inlineStr">
         <is>
-          <t>2007-08-412</t>
+          <t>2007-08-0412</t>
         </is>
       </c>
       <c r="C1196" t="inlineStr">
@@ -50606,7 +50606,7 @@
       </c>
       <c r="B1197" t="inlineStr">
         <is>
-          <t>2007-08-412</t>
+          <t>2007-08-0412</t>
         </is>
       </c>
       <c r="C1197" t="inlineStr">
@@ -50648,7 +50648,7 @@
       </c>
       <c r="B1198" t="inlineStr">
         <is>
-          <t>2007-08-413</t>
+          <t>2007-08-0413</t>
         </is>
       </c>
       <c r="C1198" t="inlineStr">
@@ -50690,7 +50690,7 @@
       </c>
       <c r="B1199" t="inlineStr">
         <is>
-          <t>2007-08-413</t>
+          <t>2007-08-0413</t>
         </is>
       </c>
       <c r="C1199" t="inlineStr">
@@ -50732,7 +50732,7 @@
       </c>
       <c r="B1200" t="inlineStr">
         <is>
-          <t>2007-08-413</t>
+          <t>2007-08-0413</t>
         </is>
       </c>
       <c r="C1200" t="inlineStr">
@@ -50774,7 +50774,7 @@
       </c>
       <c r="B1201" t="inlineStr">
         <is>
-          <t>2007-08-413</t>
+          <t>2007-08-0413</t>
         </is>
       </c>
       <c r="C1201" t="inlineStr">
@@ -50816,7 +50816,7 @@
       </c>
       <c r="B1202" t="inlineStr">
         <is>
-          <t>2007-08-413</t>
+          <t>2007-08-0413</t>
         </is>
       </c>
       <c r="C1202" t="inlineStr">
@@ -50858,7 +50858,7 @@
       </c>
       <c r="B1203" t="inlineStr">
         <is>
-          <t>2007-08-413</t>
+          <t>2007-08-0413</t>
         </is>
       </c>
       <c r="C1203" t="inlineStr">
@@ -50900,7 +50900,7 @@
       </c>
       <c r="B1204" t="inlineStr">
         <is>
-          <t>2007-08-414</t>
+          <t>2007-08-0414</t>
         </is>
       </c>
       <c r="C1204" t="inlineStr">
@@ -50942,7 +50942,7 @@
       </c>
       <c r="B1205" t="inlineStr">
         <is>
-          <t>2007-08-414</t>
+          <t>2007-08-0414</t>
         </is>
       </c>
       <c r="C1205" t="inlineStr">
@@ -50984,7 +50984,7 @@
       </c>
       <c r="B1206" t="inlineStr">
         <is>
-          <t>2007-08-414</t>
+          <t>2007-08-0414</t>
         </is>
       </c>
       <c r="C1206" t="inlineStr">
@@ -51026,7 +51026,7 @@
       </c>
       <c r="B1207" t="inlineStr">
         <is>
-          <t>2007-08-414</t>
+          <t>2007-08-0414</t>
         </is>
       </c>
       <c r="C1207" t="inlineStr">
@@ -51068,7 +51068,7 @@
       </c>
       <c r="B1208" t="inlineStr">
         <is>
-          <t>2007-08-414</t>
+          <t>2007-08-0414</t>
         </is>
       </c>
       <c r="C1208" t="inlineStr">
@@ -51110,7 +51110,7 @@
       </c>
       <c r="B1209" t="inlineStr">
         <is>
-          <t>2007-08-414</t>
+          <t>2007-08-0414</t>
         </is>
       </c>
       <c r="C1209" t="inlineStr">
@@ -51152,7 +51152,7 @@
       </c>
       <c r="B1210" t="inlineStr">
         <is>
-          <t>2007-08-414</t>
+          <t>2007-08-0414</t>
         </is>
       </c>
       <c r="C1210" t="inlineStr">
@@ -51194,7 +51194,7 @@
       </c>
       <c r="B1211" t="inlineStr">
         <is>
-          <t>2007-08-414</t>
+          <t>2007-08-0414</t>
         </is>
       </c>
       <c r="C1211" t="inlineStr">
@@ -51236,7 +51236,7 @@
       </c>
       <c r="B1212" t="inlineStr">
         <is>
-          <t>2007-08-415</t>
+          <t>2007-08-0415</t>
         </is>
       </c>
       <c r="C1212" t="inlineStr">
@@ -51278,7 +51278,7 @@
       </c>
       <c r="B1213" t="inlineStr">
         <is>
-          <t>2007-08-415</t>
+          <t>2007-08-0415</t>
         </is>
       </c>
       <c r="C1213" t="inlineStr">
@@ -51320,7 +51320,7 @@
       </c>
       <c r="B1214" t="inlineStr">
         <is>
-          <t>2007-08-415</t>
+          <t>2007-08-0415</t>
         </is>
       </c>
       <c r="C1214" t="inlineStr">
@@ -51362,7 +51362,7 @@
       </c>
       <c r="B1215" t="inlineStr">
         <is>
-          <t>2007-08-415</t>
+          <t>2007-08-0415</t>
         </is>
       </c>
       <c r="C1215" t="inlineStr">
@@ -51404,7 +51404,7 @@
       </c>
       <c r="B1216" t="inlineStr">
         <is>
-          <t>2007-08-415</t>
+          <t>2007-08-0415</t>
         </is>
       </c>
       <c r="C1216" t="inlineStr">
@@ -51446,7 +51446,7 @@
       </c>
       <c r="B1217" t="inlineStr">
         <is>
-          <t>2007-08-415</t>
+          <t>2007-08-0415</t>
         </is>
       </c>
       <c r="C1217" t="inlineStr">
@@ -51488,7 +51488,7 @@
       </c>
       <c r="B1218" t="inlineStr">
         <is>
-          <t>2007-08-416</t>
+          <t>2007-08-0416</t>
         </is>
       </c>
       <c r="C1218" t="inlineStr">
@@ -51530,7 +51530,7 @@
       </c>
       <c r="B1219" t="inlineStr">
         <is>
-          <t>2007-08-416</t>
+          <t>2007-08-0416</t>
         </is>
       </c>
       <c r="C1219" t="inlineStr">
@@ -51572,7 +51572,7 @@
       </c>
       <c r="B1220" t="inlineStr">
         <is>
-          <t>2007-08-416</t>
+          <t>2007-08-0416</t>
         </is>
       </c>
       <c r="C1220" t="inlineStr">
@@ -51614,7 +51614,7 @@
       </c>
       <c r="B1221" t="inlineStr">
         <is>
-          <t>2007-08-416</t>
+          <t>2007-08-0416</t>
         </is>
       </c>
       <c r="C1221" t="inlineStr">
@@ -51656,7 +51656,7 @@
       </c>
       <c r="B1222" t="inlineStr">
         <is>
-          <t>2007-08-416</t>
+          <t>2007-08-0416</t>
         </is>
       </c>
       <c r="C1222" t="inlineStr">
@@ -51698,7 +51698,7 @@
       </c>
       <c r="B1223" t="inlineStr">
         <is>
-          <t>2007-08-416</t>
+          <t>2007-08-0416</t>
         </is>
       </c>
       <c r="C1223" t="inlineStr">
@@ -51740,7 +51740,7 @@
       </c>
       <c r="B1224" t="inlineStr">
         <is>
-          <t>2007-08-416</t>
+          <t>2007-08-0416</t>
         </is>
       </c>
       <c r="C1224" t="inlineStr">
@@ -51782,7 +51782,7 @@
       </c>
       <c r="B1225" t="inlineStr">
         <is>
-          <t>2007-08-416</t>
+          <t>2007-08-0416</t>
         </is>
       </c>
       <c r="C1225" t="inlineStr">
@@ -51824,7 +51824,7 @@
       </c>
       <c r="B1226" t="inlineStr">
         <is>
-          <t>2007-08-416</t>
+          <t>2007-08-0416</t>
         </is>
       </c>
       <c r="C1226" t="inlineStr">
@@ -51866,7 +51866,7 @@
       </c>
       <c r="B1227" t="inlineStr">
         <is>
-          <t>2007-08-416</t>
+          <t>2007-08-0416</t>
         </is>
       </c>
       <c r="C1227" t="inlineStr">
@@ -51908,7 +51908,7 @@
       </c>
       <c r="B1228" t="inlineStr">
         <is>
-          <t>2007-08-416</t>
+          <t>2007-08-0416</t>
         </is>
       </c>
       <c r="C1228" t="inlineStr">
@@ -51950,7 +51950,7 @@
       </c>
       <c r="B1229" t="inlineStr">
         <is>
-          <t>2007-08-416</t>
+          <t>2007-08-0416</t>
         </is>
       </c>
       <c r="C1229" t="inlineStr">
@@ -51992,7 +51992,7 @@
       </c>
       <c r="B1230" t="inlineStr">
         <is>
-          <t>2007-08-416</t>
+          <t>2007-08-0416</t>
         </is>
       </c>
       <c r="C1230" t="inlineStr">
@@ -52034,7 +52034,7 @@
       </c>
       <c r="B1231" t="inlineStr">
         <is>
-          <t>2007-08-416</t>
+          <t>2007-08-0416</t>
         </is>
       </c>
       <c r="C1231" t="inlineStr">
@@ -52076,7 +52076,7 @@
       </c>
       <c r="B1232" t="inlineStr">
         <is>
-          <t>2007-08-419</t>
+          <t>2007-08-0419</t>
         </is>
       </c>
       <c r="C1232" t="inlineStr">
@@ -52118,7 +52118,7 @@
       </c>
       <c r="B1233" t="inlineStr">
         <is>
-          <t>2007-08-419</t>
+          <t>2007-08-0419</t>
         </is>
       </c>
       <c r="C1233" t="inlineStr">
@@ -52160,7 +52160,7 @@
       </c>
       <c r="B1234" t="inlineStr">
         <is>
-          <t>2007-08-419</t>
+          <t>2007-08-0419</t>
         </is>
       </c>
       <c r="C1234" t="inlineStr">
@@ -52202,7 +52202,7 @@
       </c>
       <c r="B1235" t="inlineStr">
         <is>
-          <t>2007-08-419</t>
+          <t>2007-08-0419</t>
         </is>
       </c>
       <c r="C1235" t="inlineStr">
@@ -52244,7 +52244,7 @@
       </c>
       <c r="B1236" t="inlineStr">
         <is>
-          <t>2007-08-420</t>
+          <t>2007-08-0420</t>
         </is>
       </c>
       <c r="C1236" t="inlineStr">
@@ -52286,7 +52286,7 @@
       </c>
       <c r="B1237" t="inlineStr">
         <is>
-          <t>2007-08-420</t>
+          <t>2007-08-0420</t>
         </is>
       </c>
       <c r="C1237" t="inlineStr">
@@ -52328,7 +52328,7 @@
       </c>
       <c r="B1238" t="inlineStr">
         <is>
-          <t>2007-08-420</t>
+          <t>2007-08-0420</t>
         </is>
       </c>
       <c r="C1238" t="inlineStr">
@@ -52370,7 +52370,7 @@
       </c>
       <c r="B1239" t="inlineStr">
         <is>
-          <t>2007-08-420</t>
+          <t>2007-08-0420</t>
         </is>
       </c>
       <c r="C1239" t="inlineStr">
@@ -52412,7 +52412,7 @@
       </c>
       <c r="B1240" t="inlineStr">
         <is>
-          <t>2007-08-421</t>
+          <t>2007-08-0421</t>
         </is>
       </c>
       <c r="C1240" t="inlineStr">
@@ -52454,7 +52454,7 @@
       </c>
       <c r="B1241" t="inlineStr">
         <is>
-          <t>2007-08-421</t>
+          <t>2007-08-0421</t>
         </is>
       </c>
       <c r="C1241" t="inlineStr">
@@ -52496,7 +52496,7 @@
       </c>
       <c r="B1242" t="inlineStr">
         <is>
-          <t>2007-08-422</t>
+          <t>2007-08-0422</t>
         </is>
       </c>
       <c r="C1242" t="inlineStr">
@@ -52538,7 +52538,7 @@
       </c>
       <c r="B1243" t="inlineStr">
         <is>
-          <t>2007-08-422</t>
+          <t>2007-08-0422</t>
         </is>
       </c>
       <c r="C1243" t="inlineStr">
@@ -52580,7 +52580,7 @@
       </c>
       <c r="B1244" t="inlineStr">
         <is>
-          <t>2007-08-422</t>
+          <t>2007-08-0422</t>
         </is>
       </c>
       <c r="C1244" t="inlineStr">
@@ -52622,7 +52622,7 @@
       </c>
       <c r="B1245" t="inlineStr">
         <is>
-          <t>2007-08-423</t>
+          <t>2007-08-0423</t>
         </is>
       </c>
       <c r="C1245" t="inlineStr">
@@ -52664,7 +52664,7 @@
       </c>
       <c r="B1246" t="inlineStr">
         <is>
-          <t>2007-08-423</t>
+          <t>2007-08-0423</t>
         </is>
       </c>
       <c r="C1246" t="inlineStr">
@@ -52706,7 +52706,7 @@
       </c>
       <c r="B1247" t="inlineStr">
         <is>
-          <t>2007-08-423</t>
+          <t>2007-08-0423</t>
         </is>
       </c>
       <c r="C1247" t="inlineStr">
@@ -52748,7 +52748,7 @@
       </c>
       <c r="B1248" t="inlineStr">
         <is>
-          <t>2007-08-424</t>
+          <t>2007-08-0424</t>
         </is>
       </c>
       <c r="C1248" t="inlineStr">
@@ -52790,7 +52790,7 @@
       </c>
       <c r="B1249" t="inlineStr">
         <is>
-          <t>2007-08-424</t>
+          <t>2007-08-0424</t>
         </is>
       </c>
       <c r="C1249" t="inlineStr">
@@ -52832,7 +52832,7 @@
       </c>
       <c r="B1250" t="inlineStr">
         <is>
-          <t>2007-08-424</t>
+          <t>2007-08-0424</t>
         </is>
       </c>
       <c r="C1250" t="inlineStr">
@@ -52874,7 +52874,7 @@
       </c>
       <c r="B1251" t="inlineStr">
         <is>
-          <t>2007-08-425</t>
+          <t>2007-08-0425</t>
         </is>
       </c>
       <c r="C1251" t="inlineStr">
@@ -52916,7 +52916,7 @@
       </c>
       <c r="B1252" t="inlineStr">
         <is>
-          <t>2007-08-425</t>
+          <t>2007-08-0425</t>
         </is>
       </c>
       <c r="C1252" t="inlineStr">
@@ -52958,7 +52958,7 @@
       </c>
       <c r="B1253" t="inlineStr">
         <is>
-          <t>2007-08-425</t>
+          <t>2007-08-0425</t>
         </is>
       </c>
       <c r="C1253" t="inlineStr">
@@ -53000,7 +53000,7 @@
       </c>
       <c r="B1254" t="inlineStr">
         <is>
-          <t>2007-08-426</t>
+          <t>2007-08-0426</t>
         </is>
       </c>
       <c r="C1254" t="inlineStr">
@@ -53042,7 +53042,7 @@
       </c>
       <c r="B1255" t="inlineStr">
         <is>
-          <t>2007-08-426</t>
+          <t>2007-08-0426</t>
         </is>
       </c>
       <c r="C1255" t="inlineStr">
@@ -53084,7 +53084,7 @@
       </c>
       <c r="B1256" t="inlineStr">
         <is>
-          <t>2007-08-426</t>
+          <t>2007-08-0426</t>
         </is>
       </c>
       <c r="C1256" t="inlineStr">
@@ -53126,7 +53126,7 @@
       </c>
       <c r="B1257" t="inlineStr">
         <is>
-          <t>2007-08-426</t>
+          <t>2007-08-0426</t>
         </is>
       </c>
       <c r="C1257" t="inlineStr">
@@ -53168,7 +53168,7 @@
       </c>
       <c r="B1258" t="inlineStr">
         <is>
-          <t>2007-08-427</t>
+          <t>2007-08-0427</t>
         </is>
       </c>
       <c r="C1258" t="inlineStr">
@@ -53210,7 +53210,7 @@
       </c>
       <c r="B1259" t="inlineStr">
         <is>
-          <t>2007-08-427</t>
+          <t>2007-08-0427</t>
         </is>
       </c>
       <c r="C1259" t="inlineStr">
@@ -53252,7 +53252,7 @@
       </c>
       <c r="B1260" t="inlineStr">
         <is>
-          <t>2007-08-427</t>
+          <t>2007-08-0427</t>
         </is>
       </c>
       <c r="C1260" t="inlineStr">
@@ -53294,7 +53294,7 @@
       </c>
       <c r="B1261" t="inlineStr">
         <is>
-          <t>2007-08-427</t>
+          <t>2007-08-0427</t>
         </is>
       </c>
       <c r="C1261" t="inlineStr">
@@ -53336,7 +53336,7 @@
       </c>
       <c r="B1262" t="inlineStr">
         <is>
-          <t>2007-08-428</t>
+          <t>2007-08-0428</t>
         </is>
       </c>
       <c r="C1262" t="inlineStr">
@@ -53378,7 +53378,7 @@
       </c>
       <c r="B1263" t="inlineStr">
         <is>
-          <t>2007-08-428</t>
+          <t>2007-08-0428</t>
         </is>
       </c>
       <c r="C1263" t="inlineStr">
@@ -53420,7 +53420,7 @@
       </c>
       <c r="B1264" t="inlineStr">
         <is>
-          <t>2007-08-428</t>
+          <t>2007-08-0428</t>
         </is>
       </c>
       <c r="C1264" t="inlineStr">
@@ -53462,7 +53462,7 @@
       </c>
       <c r="B1265" t="inlineStr">
         <is>
-          <t>2007-08-429</t>
+          <t>2007-08-0429</t>
         </is>
       </c>
       <c r="C1265" t="inlineStr">
@@ -53504,7 +53504,7 @@
       </c>
       <c r="B1266" t="inlineStr">
         <is>
-          <t>2007-08-429</t>
+          <t>2007-08-0429</t>
         </is>
       </c>
       <c r="C1266" t="inlineStr">
@@ -53546,7 +53546,7 @@
       </c>
       <c r="B1267" t="inlineStr">
         <is>
-          <t>2007-08-429</t>
+          <t>2007-08-0429</t>
         </is>
       </c>
       <c r="C1267" t="inlineStr">
@@ -53588,7 +53588,7 @@
       </c>
       <c r="B1268" t="inlineStr">
         <is>
-          <t>2007-08-429</t>
+          <t>2007-08-0429</t>
         </is>
       </c>
       <c r="C1268" t="inlineStr">
@@ -53630,7 +53630,7 @@
       </c>
       <c r="B1269" t="inlineStr">
         <is>
-          <t>2007-08-430</t>
+          <t>2007-08-0430</t>
         </is>
       </c>
       <c r="C1269" t="inlineStr">
@@ -53672,7 +53672,7 @@
       </c>
       <c r="B1270" t="inlineStr">
         <is>
-          <t>2007-08-430</t>
+          <t>2007-08-0430</t>
         </is>
       </c>
       <c r="C1270" t="inlineStr">
@@ -53714,7 +53714,7 @@
       </c>
       <c r="B1271" t="inlineStr">
         <is>
-          <t>2007-08-501</t>
+          <t>2007-08-0501</t>
         </is>
       </c>
       <c r="C1271" t="inlineStr">
@@ -53756,7 +53756,7 @@
       </c>
       <c r="B1272" t="inlineStr">
         <is>
-          <t>2007-08-502</t>
+          <t>2007-08-0502</t>
         </is>
       </c>
       <c r="C1272" t="inlineStr">
@@ -53798,7 +53798,7 @@
       </c>
       <c r="B1273" t="inlineStr">
         <is>
-          <t>2007-08-502</t>
+          <t>2007-08-0502</t>
         </is>
       </c>
       <c r="C1273" t="inlineStr">
@@ -53840,7 +53840,7 @@
       </c>
       <c r="B1274" t="inlineStr">
         <is>
-          <t>2007-08-502</t>
+          <t>2007-08-0502</t>
         </is>
       </c>
       <c r="C1274" t="inlineStr">
@@ -53882,7 +53882,7 @@
       </c>
       <c r="B1275" t="inlineStr">
         <is>
-          <t>2007-08-503</t>
+          <t>2007-08-0503</t>
         </is>
       </c>
       <c r="C1275" t="inlineStr">
@@ -53924,7 +53924,7 @@
       </c>
       <c r="B1276" t="inlineStr">
         <is>
-          <t>2007-08-503</t>
+          <t>2007-08-0503</t>
         </is>
       </c>
       <c r="C1276" t="inlineStr">
@@ -53966,7 +53966,7 @@
       </c>
       <c r="B1277" t="inlineStr">
         <is>
-          <t>2007-08-504</t>
+          <t>2007-08-0504</t>
         </is>
       </c>
       <c r="C1277" t="inlineStr">
@@ -54008,7 +54008,7 @@
       </c>
       <c r="B1278" t="inlineStr">
         <is>
-          <t>2007-08-504</t>
+          <t>2007-08-0504</t>
         </is>
       </c>
       <c r="C1278" t="inlineStr">
@@ -54050,7 +54050,7 @@
       </c>
       <c r="B1279" t="inlineStr">
         <is>
-          <t>2007-08-505</t>
+          <t>2007-08-0505</t>
         </is>
       </c>
       <c r="C1279" t="inlineStr">
@@ -54092,7 +54092,7 @@
       </c>
       <c r="B1280" t="inlineStr">
         <is>
-          <t>2007-08-505</t>
+          <t>2007-08-0505</t>
         </is>
       </c>
       <c r="C1280" t="inlineStr">
@@ -54134,7 +54134,7 @@
       </c>
       <c r="B1281" t="inlineStr">
         <is>
-          <t>2007-08-506</t>
+          <t>2007-08-0506</t>
         </is>
       </c>
       <c r="C1281" t="inlineStr">
@@ -54176,7 +54176,7 @@
       </c>
       <c r="B1282" t="inlineStr">
         <is>
-          <t>2007-08-507</t>
+          <t>2007-08-0507</t>
         </is>
       </c>
       <c r="C1282" t="inlineStr">
@@ -54218,7 +54218,7 @@
       </c>
       <c r="B1283" t="inlineStr">
         <is>
-          <t>2007-08-507</t>
+          <t>2007-08-0507</t>
         </is>
       </c>
       <c r="C1283" t="inlineStr">
@@ -54260,7 +54260,7 @@
       </c>
       <c r="B1284" t="inlineStr">
         <is>
-          <t>2007-08-508</t>
+          <t>2007-08-0508</t>
         </is>
       </c>
       <c r="C1284" t="inlineStr">
@@ -54302,7 +54302,7 @@
       </c>
       <c r="B1285" t="inlineStr">
         <is>
-          <t>2007-08-508</t>
+          <t>2007-08-0508</t>
         </is>
       </c>
       <c r="C1285" t="inlineStr">
@@ -54344,7 +54344,7 @@
       </c>
       <c r="B1286" t="inlineStr">
         <is>
-          <t>2007-08-509</t>
+          <t>2007-08-0509</t>
         </is>
       </c>
       <c r="C1286" t="inlineStr">
@@ -54386,7 +54386,7 @@
       </c>
       <c r="B1287" t="inlineStr">
         <is>
-          <t>2007-08-510</t>
+          <t>2007-08-0510</t>
         </is>
       </c>
       <c r="C1287" t="inlineStr">
@@ -54428,7 +54428,7 @@
       </c>
       <c r="B1288" t="inlineStr">
         <is>
-          <t>2007-08-510</t>
+          <t>2007-08-0510</t>
         </is>
       </c>
       <c r="C1288" t="inlineStr">
@@ -54470,7 +54470,7 @@
       </c>
       <c r="B1289" t="inlineStr">
         <is>
-          <t>2007-08-511</t>
+          <t>2007-08-0511</t>
         </is>
       </c>
       <c r="C1289" t="inlineStr">
@@ -54512,7 +54512,7 @@
       </c>
       <c r="B1290" t="inlineStr">
         <is>
-          <t>2007-08-511</t>
+          <t>2007-08-0511</t>
         </is>
       </c>
       <c r="C1290" t="inlineStr">
@@ -54554,7 +54554,7 @@
       </c>
       <c r="B1291" t="inlineStr">
         <is>
-          <t>2007-08-512</t>
+          <t>2007-08-0512</t>
         </is>
       </c>
       <c r="C1291" t="inlineStr">
@@ -54596,7 +54596,7 @@
       </c>
       <c r="B1292" t="inlineStr">
         <is>
-          <t>2007-08-513</t>
+          <t>2007-08-0513</t>
         </is>
       </c>
       <c r="C1292" t="inlineStr">
@@ -54638,7 +54638,7 @@
       </c>
       <c r="B1293" t="inlineStr">
         <is>
-          <t>2007-08-513</t>
+          <t>2007-08-0513</t>
         </is>
       </c>
       <c r="C1293" t="inlineStr">
@@ -54680,7 +54680,7 @@
       </c>
       <c r="B1294" t="inlineStr">
         <is>
-          <t>2007-08-514</t>
+          <t>2007-08-0514</t>
         </is>
       </c>
       <c r="C1294" t="inlineStr">
@@ -54722,7 +54722,7 @@
       </c>
       <c r="B1295" t="inlineStr">
         <is>
-          <t>2007-08-514</t>
+          <t>2007-08-0514</t>
         </is>
       </c>
       <c r="C1295" t="inlineStr">
@@ -54764,7 +54764,7 @@
       </c>
       <c r="B1296" t="inlineStr">
         <is>
-          <t>2007-08-515</t>
+          <t>2007-08-0515</t>
         </is>
       </c>
       <c r="C1296" t="inlineStr">
@@ -54806,7 +54806,7 @@
       </c>
       <c r="B1297" t="inlineStr">
         <is>
-          <t>2007-08-516</t>
+          <t>2007-08-0516</t>
         </is>
       </c>
       <c r="C1297" t="inlineStr">
@@ -54848,7 +54848,7 @@
       </c>
       <c r="B1298" t="inlineStr">
         <is>
-          <t>2007-08-516</t>
+          <t>2007-08-0516</t>
         </is>
       </c>
       <c r="C1298" t="inlineStr">
@@ -54890,7 +54890,7 @@
       </c>
       <c r="B1299" t="inlineStr">
         <is>
-          <t>2007-08-518</t>
+          <t>2007-08-0518</t>
         </is>
       </c>
       <c r="C1299" t="inlineStr">
@@ -54932,7 +54932,7 @@
       </c>
       <c r="B1300" t="inlineStr">
         <is>
-          <t>2007-08-519</t>
+          <t>2007-08-0519</t>
         </is>
       </c>
       <c r="C1300" t="inlineStr">
@@ -54974,7 +54974,7 @@
       </c>
       <c r="B1301" t="inlineStr">
         <is>
-          <t>2007-08-520</t>
+          <t>2007-08-0520</t>
         </is>
       </c>
       <c r="C1301" t="inlineStr">
@@ -55016,7 +55016,7 @@
       </c>
       <c r="B1302" t="inlineStr">
         <is>
-          <t>2007-08-521</t>
+          <t>2007-08-0521</t>
         </is>
       </c>
       <c r="C1302" t="inlineStr">
@@ -55058,7 +55058,7 @@
       </c>
       <c r="B1303" t="inlineStr">
         <is>
-          <t>2007-08-522</t>
+          <t>2007-08-0522</t>
         </is>
       </c>
       <c r="C1303" t="inlineStr">
@@ -55100,7 +55100,7 @@
       </c>
       <c r="B1304" t="inlineStr">
         <is>
-          <t>2007-08-523</t>
+          <t>2007-08-0523</t>
         </is>
       </c>
       <c r="C1304" t="inlineStr">
@@ -55142,7 +55142,7 @@
       </c>
       <c r="B1305" t="inlineStr">
         <is>
-          <t>2007-08-524</t>
+          <t>2007-08-0524</t>
         </is>
       </c>
       <c r="C1305" t="inlineStr">
@@ -55184,7 +55184,7 @@
       </c>
       <c r="B1306" t="inlineStr">
         <is>
-          <t>2007-08-525</t>
+          <t>2007-08-0525</t>
         </is>
       </c>
       <c r="C1306" t="inlineStr">
@@ -55226,7 +55226,7 @@
       </c>
       <c r="B1307" t="inlineStr">
         <is>
-          <t>2007-08-526</t>
+          <t>2007-08-0526</t>
         </is>
       </c>
       <c r="C1307" t="inlineStr">
@@ -55268,7 +55268,7 @@
       </c>
       <c r="B1308" t="inlineStr">
         <is>
-          <t>2007-08-527</t>
+          <t>2007-08-0527</t>
         </is>
       </c>
       <c r="C1308" t="inlineStr">
@@ -55310,7 +55310,7 @@
       </c>
       <c r="B1309" t="inlineStr">
         <is>
-          <t>2007-08-528</t>
+          <t>2007-08-0528</t>
         </is>
       </c>
       <c r="C1309" t="inlineStr">
@@ -55352,7 +55352,7 @@
       </c>
       <c r="B1310" t="inlineStr">
         <is>
-          <t>2007-08-529</t>
+          <t>2007-08-0529</t>
         </is>
       </c>
       <c r="C1310" t="inlineStr">
@@ -55394,7 +55394,7 @@
       </c>
       <c r="B1311" t="inlineStr">
         <is>
-          <t>2007-08-530</t>
+          <t>2007-08-0530</t>
         </is>
       </c>
       <c r="C1311" t="inlineStr">
@@ -55436,7 +55436,7 @@
       </c>
       <c r="B1312" t="inlineStr">
         <is>
-          <t>2007-08-605</t>
+          <t>2007-08-0605</t>
         </is>
       </c>
       <c r="C1312" t="inlineStr">
@@ -55478,7 +55478,7 @@
       </c>
       <c r="B1313" t="inlineStr">
         <is>
-          <t>2007-08-608</t>
+          <t>2007-08-0608</t>
         </is>
       </c>
       <c r="C1313" t="inlineStr">
@@ -55520,7 +55520,7 @@
       </c>
       <c r="B1314" t="inlineStr">
         <is>
-          <t>2007-08-610</t>
+          <t>2007-08-0610</t>
         </is>
       </c>
       <c r="C1314" t="inlineStr">
@@ -55562,7 +55562,7 @@
       </c>
       <c r="B1315" t="inlineStr">
         <is>
-          <t>2007-08-612</t>
+          <t>2007-08-0612</t>
         </is>
       </c>
       <c r="C1315" t="inlineStr">
@@ -55604,7 +55604,7 @@
       </c>
       <c r="B1316" t="inlineStr">
         <is>
-          <t>2007-08-615</t>
+          <t>2007-08-0615</t>
         </is>
       </c>
       <c r="C1316" t="inlineStr">
@@ -55646,7 +55646,7 @@
       </c>
       <c r="B1317" t="inlineStr">
         <is>
-          <t>2007-08-617</t>
+          <t>2007-08-0617</t>
         </is>
       </c>
       <c r="C1317" t="inlineStr">

--- a/Odds-Data-Clean/2007-08.xlsx
+++ b/Odds-Data-Clean/2007-08.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -54,18 +54,18 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
@@ -55683,6 +55683,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>